--- a/NL2SPARQL_Evaluation_Dataset.xlsx
+++ b/NL2SPARQL_Evaluation_Dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fersi\Desktop\NL2SPARQL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{853AFEA8-69C9-48CE-9757-431F01C16CCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{143BA9D6-44A1-4013-8F0D-EFB2787C32F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="26640" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="13410" windowHeight="14235" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Legend" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="436">
   <si>
     <t>NL2SPARQL Evaluation Dataset — Legend</t>
   </si>
@@ -968,9 +968,6 @@
     <t>قارن ارتفاع مطاري BLQ وNAP.</t>
   </si>
   <si>
-    <t>BLQ: 123, NAP: 294</t>
-  </si>
-  <si>
     <t>Verified from kg2 sample. Two-value comparison — Exact Match scoring may be strict on format; F1 is the more meaningful metric here.</t>
   </si>
   <si>
@@ -986,9 +983,6 @@
     <t>قارن طول مدرج مطاري KRK وLUX.</t>
   </si>
   <si>
-    <t>KRK: 8366, LUX: 13123</t>
-  </si>
-  <si>
     <t>compare_two_airports_003</t>
   </si>
   <si>
@@ -1001,9 +995,6 @@
     <t>قارن ارتفاع مطاري CHQ وSOF.</t>
   </si>
   <si>
-    <t>CHQ: 490, SOF: 1742</t>
-  </si>
-  <si>
     <t>out_of_scope_001</t>
   </si>
   <si>
@@ -1299,6 +1290,48 @@
   </si>
   <si>
     <t>1+B36:B37</t>
+  </si>
+  <si>
+    <t>ESB, SOF, SBZ (in that order, highest first)</t>
+  </si>
+  <si>
+    <t>STR</t>
+  </si>
+  <si>
+    <t>BKK, VCE, LCA, GYD, BCN (lowest first)</t>
+  </si>
+  <si>
+    <t>NAP is higher (BLQ: 123, NAP: 294)</t>
+  </si>
+  <si>
+    <t>LUX is longer (KRK: 8366, LUX: 13123)</t>
+  </si>
+  <si>
+    <t>SOF is higher (CHQ: 490, SOF: 1742)</t>
+  </si>
+  <si>
+    <t>AI180, PC904, OS631, BR62, OS830, OS315, OS631, 7L280, OS87, OS52 (top 10 by gspeed, highest first)</t>
+  </si>
+  <si>
+    <t>LO225, TO4388, EW9754, FR6889, OU442, FR1589, OS462, AY1475, PE106, FR947</t>
+  </si>
+  <si>
+    <t>AI180, PC904, OS631, BR62, OS830, OS315, OS631, 7L280, OS87, OS52</t>
+  </si>
+  <si>
+    <t>ESB, SOF, SBZ, MUC, ZRH, EBL, ACH, STR, LUX, GRZ</t>
+  </si>
+  <si>
+    <t>EBL, JFK, CDG, CDG, IST, IST, BER, FRA, FRA, FRA</t>
+  </si>
+  <si>
+    <t>PFO, CTA, BOM, RIX, PMI, CPH, FCO, JFK, BCN, GYD</t>
+  </si>
+  <si>
+    <t>Bari Karol Wojtyła International Airport, Bologna Guglielmo Marconi Airport, Catania-Fontanarossa Airport, Falcone–Borsellino Airport, Naples International Airport, Rome–Fiumicino Leonardo da Vinci International Airport, Venice Marco Polo Airport (all 7 — Italy has fewer than the 10-limit, so this is the complete answer)</t>
+  </si>
+  <si>
+    <t>Chania International Airport, Kos International Airport "Ippokratis" (complete — Greece only has 2)</t>
   </si>
 </sst>
 </file>
@@ -1389,7 +1422,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1414,12 +1447,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1433,6 +1460,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1954,15 +1984,15 @@
   <dimension ref="A1:L73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25" style="15" customWidth="1"/>
+    <col min="1" max="1" width="25" style="13" customWidth="1"/>
     <col min="2" max="2" width="6" style="10" customWidth="1"/>
-    <col min="3" max="3" width="22" style="10" customWidth="1"/>
-    <col min="4" max="4" width="12" style="15" customWidth="1"/>
-    <col min="5" max="5" width="16" style="15" customWidth="1"/>
-    <col min="6" max="6" width="20" style="15" customWidth="1"/>
-    <col min="7" max="7" width="12" style="15" customWidth="1"/>
-    <col min="8" max="10" width="46" style="15" customWidth="1"/>
-    <col min="11" max="11" width="22" style="15" customWidth="1"/>
+    <col min="3" max="3" width="22" style="13" customWidth="1"/>
+    <col min="4" max="4" width="12" style="13" customWidth="1"/>
+    <col min="5" max="5" width="16" style="13" customWidth="1"/>
+    <col min="6" max="6" width="20" style="13" customWidth="1"/>
+    <col min="7" max="7" width="12" style="13" customWidth="1"/>
+    <col min="8" max="10" width="46" style="13" customWidth="1"/>
+    <col min="11" max="11" width="46.42578125" style="13" customWidth="1"/>
     <col min="12" max="12" width="30" style="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2005,7 +2035,7 @@
       </c>
     </row>
     <row r="2" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="11" t="s">
         <v>44</v>
       </c>
       <c r="B2" s="8">
@@ -2014,34 +2044,34 @@
       <c r="C2" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13" t="s">
+      <c r="F2" s="11"/>
+      <c r="G2" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="J2" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="K2" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="17" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="12" t="s">
         <v>53</v>
       </c>
       <c r="B3" s="9">
@@ -2050,34 +2080,34 @@
       <c r="C3" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14" t="s">
+      <c r="F3" s="12"/>
+      <c r="G3" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="I3" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="J3" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="K3" s="17" t="s">
+      <c r="K3" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="L3" s="19" t="s">
+      <c r="L3" s="18" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="12" t="s">
         <v>59</v>
       </c>
       <c r="B4" s="9">
@@ -2086,34 +2116,34 @@
       <c r="C4" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14" t="s">
+      <c r="F4" s="12"/>
+      <c r="G4" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H4" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="I4" s="17" t="s">
+      <c r="I4" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="J4" s="17" t="s">
+      <c r="J4" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="K4" s="17" t="s">
+      <c r="K4" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="L4" s="19" t="s">
+      <c r="L4" s="18" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="12" t="s">
         <v>64</v>
       </c>
       <c r="B5" s="9">
@@ -2122,34 +2152,34 @@
       <c r="C5" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14" t="s">
+      <c r="F5" s="12"/>
+      <c r="G5" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="I5" s="17" t="s">
+      <c r="I5" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="J5" s="17" t="s">
+      <c r="J5" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="K5" s="17">
+      <c r="K5" s="15">
         <v>400</v>
       </c>
-      <c r="L5" s="19" t="s">
+      <c r="L5" s="18" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="12" t="s">
         <v>70</v>
       </c>
       <c r="B6" s="9">
@@ -2158,34 +2188,34 @@
       <c r="C6" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14" t="s">
+      <c r="F6" s="12"/>
+      <c r="G6" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="I6" s="17" t="s">
+      <c r="I6" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="J6" s="17" t="s">
+      <c r="J6" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="K6" s="17" t="s">
+      <c r="K6" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="L6" s="19" t="s">
+      <c r="L6" s="18" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="12" t="s">
         <v>76</v>
       </c>
       <c r="B7" s="9">
@@ -2194,34 +2224,34 @@
       <c r="C7" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14" t="s">
+      <c r="F7" s="12"/>
+      <c r="G7" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="I7" s="17" t="s">
+      <c r="I7" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="J7" s="17" t="s">
+      <c r="J7" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="K7" s="17" t="s">
-        <v>420</v>
-      </c>
-      <c r="L7" s="19" t="s">
+      <c r="K7" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="L7" s="18" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="12" t="s">
         <v>81</v>
       </c>
       <c r="B8" s="9">
@@ -2230,34 +2260,34 @@
       <c r="C8" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14" t="s">
+      <c r="F8" s="12"/>
+      <c r="G8" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="H8" s="17" t="s">
+      <c r="H8" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="I8" s="17" t="s">
+      <c r="I8" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="J8" s="17" t="s">
+      <c r="J8" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="K8" s="17" t="s">
+      <c r="K8" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="L8" s="19" t="s">
+      <c r="L8" s="18" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="12" t="s">
         <v>86</v>
       </c>
       <c r="B9" s="9">
@@ -2266,34 +2296,34 @@
       <c r="C9" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14" t="s">
+      <c r="F9" s="12"/>
+      <c r="G9" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="H9" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="I9" s="17" t="s">
+      <c r="I9" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="J9" s="17" t="s">
+      <c r="J9" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="K9" s="17" t="s">
+      <c r="K9" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="L9" s="19" t="s">
+      <c r="L9" s="18" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="12" t="s">
         <v>90</v>
       </c>
       <c r="B10" s="9">
@@ -2302,34 +2332,34 @@
       <c r="C10" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14" t="s">
+      <c r="F10" s="12"/>
+      <c r="G10" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="H10" s="17" t="s">
+      <c r="H10" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="I10" s="17" t="s">
+      <c r="I10" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="J10" s="17" t="s">
+      <c r="J10" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="K10" s="17" t="s">
+      <c r="K10" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="L10" s="19" t="s">
+      <c r="L10" s="18" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="11" t="s">
         <v>95</v>
       </c>
       <c r="B11" s="8">
@@ -2338,34 +2368,34 @@
       <c r="C11" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13" t="s">
+      <c r="F11" s="11"/>
+      <c r="G11" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="16" t="s">
+      <c r="H11" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="I11" s="16" t="s">
+      <c r="I11" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="J11" s="16" t="s">
+      <c r="J11" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="K11" s="16" t="s">
+      <c r="K11" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="L11" s="18" t="s">
+      <c r="L11" s="17" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="12" t="s">
         <v>103</v>
       </c>
       <c r="B12" s="9">
@@ -2374,34 +2404,34 @@
       <c r="C12" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14" t="s">
+      <c r="F12" s="12"/>
+      <c r="G12" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="H12" s="17" t="s">
+      <c r="H12" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="I12" s="17" t="s">
+      <c r="I12" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="J12" s="17" t="s">
+      <c r="J12" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="K12" s="17" t="s">
+      <c r="K12" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="L12" s="19" t="s">
+      <c r="L12" s="18" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="12" t="s">
         <v>109</v>
       </c>
       <c r="B13" s="9">
@@ -2410,34 +2440,34 @@
       <c r="C13" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14" t="s">
+      <c r="F13" s="12"/>
+      <c r="G13" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="H13" s="17" t="s">
+      <c r="H13" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="I13" s="17" t="s">
+      <c r="I13" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="J13" s="17" t="s">
+      <c r="J13" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="K13" s="17" t="s">
+      <c r="K13" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="L13" s="19" t="s">
+      <c r="L13" s="18" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="12" t="s">
         <v>115</v>
       </c>
       <c r="B14" s="9">
@@ -2446,34 +2476,34 @@
       <c r="C14" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14" t="s">
+      <c r="F14" s="12"/>
+      <c r="G14" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="17" t="s">
+      <c r="H14" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="I14" s="17" t="s">
+      <c r="I14" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="J14" s="17" t="s">
+      <c r="J14" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="K14" s="17" t="s">
+      <c r="K14" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="L14" s="19" t="s">
+      <c r="L14" s="18" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="12" t="s">
         <v>121</v>
       </c>
       <c r="B15" s="9">
@@ -2482,34 +2512,34 @@
       <c r="C15" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14" t="s">
+      <c r="F15" s="12"/>
+      <c r="G15" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="17" t="s">
+      <c r="H15" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="I15" s="17" t="s">
+      <c r="I15" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="J15" s="17" t="s">
+      <c r="J15" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="K15" s="17" t="s">
+      <c r="K15" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="L15" s="19" t="s">
+      <c r="L15" s="18" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="51" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="12" t="s">
         <v>127</v>
       </c>
       <c r="B16" s="9">
@@ -2518,34 +2548,34 @@
       <c r="C16" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14" t="s">
+      <c r="F16" s="12"/>
+      <c r="G16" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="H16" s="17" t="s">
+      <c r="H16" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="I16" s="17" t="s">
+      <c r="I16" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="J16" s="17" t="s">
+      <c r="J16" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="K16" s="17" t="s">
-        <v>421</v>
-      </c>
-      <c r="L16" s="19" t="s">
+      <c r="K16" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="L16" s="18" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="12" t="s">
         <v>132</v>
       </c>
       <c r="B17" s="9">
@@ -2554,34 +2584,34 @@
       <c r="C17" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14" t="s">
+      <c r="F17" s="12"/>
+      <c r="G17" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="H17" s="17" t="s">
+      <c r="H17" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="I17" s="17" t="s">
+      <c r="I17" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="J17" s="17" t="s">
+      <c r="J17" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="K17" s="17" t="s">
+      <c r="K17" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="L17" s="19" t="s">
+      <c r="L17" s="18" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="12" t="s">
         <v>137</v>
       </c>
       <c r="B18" s="9">
@@ -2590,34 +2620,34 @@
       <c r="C18" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14" t="s">
+      <c r="F18" s="12"/>
+      <c r="G18" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="H18" s="17" t="s">
+      <c r="H18" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="I18" s="17" t="s">
+      <c r="I18" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="J18" s="17" t="s">
+      <c r="J18" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="K18" s="17" t="s">
+      <c r="K18" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="L18" s="19" t="s">
+      <c r="L18" s="18" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="12" t="s">
         <v>141</v>
       </c>
       <c r="B19" s="9">
@@ -2626,34 +2656,34 @@
       <c r="C19" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14" t="s">
+      <c r="F19" s="12"/>
+      <c r="G19" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="H19" s="17" t="s">
+      <c r="H19" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="I19" s="17" t="s">
+      <c r="I19" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="J19" s="17" t="s">
+      <c r="J19" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="K19" s="17" t="s">
+      <c r="K19" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="L19" s="19" t="s">
+      <c r="L19" s="18" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="11" t="s">
         <v>147</v>
       </c>
       <c r="B20" s="8">
@@ -2662,34 +2692,34 @@
       <c r="C20" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="H20" s="16" t="s">
+      <c r="F20" s="11"/>
+      <c r="G20" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="H20" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="I20" s="16" t="s">
+      <c r="I20" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="J20" s="16" t="s">
+      <c r="J20" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="K20" s="16" t="s">
-        <v>422</v>
-      </c>
-      <c r="L20" s="18" t="s">
+      <c r="K20" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="L20" s="17" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="12" t="s">
         <v>155</v>
       </c>
       <c r="B21" s="9">
@@ -2698,34 +2728,34 @@
       <c r="C21" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H21" s="17" t="s">
+      <c r="F21" s="12"/>
+      <c r="G21" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H21" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="I21" s="17" t="s">
+      <c r="I21" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="J21" s="17" t="s">
+      <c r="J21" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="K21" s="17" t="s">
+      <c r="K21" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="L21" s="19" t="s">
+      <c r="L21" s="18" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="12" t="s">
         <v>161</v>
       </c>
       <c r="B22" s="9">
@@ -2734,34 +2764,34 @@
       <c r="C22" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H22" s="17" t="s">
+      <c r="F22" s="12"/>
+      <c r="G22" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H22" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="I22" s="17" t="s">
+      <c r="I22" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="J22" s="17" t="s">
+      <c r="J22" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="K22" s="17" t="s">
+      <c r="K22" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="L22" s="19" t="s">
+      <c r="L22" s="18" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="12" t="s">
         <v>166</v>
       </c>
       <c r="B23" s="9">
@@ -2770,34 +2800,34 @@
       <c r="C23" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H23" s="17" t="s">
+      <c r="F23" s="12"/>
+      <c r="G23" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H23" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="I23" s="17" t="s">
+      <c r="I23" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="J23" s="17" t="s">
+      <c r="J23" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="K23" s="17" t="s">
+      <c r="K23" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="L23" s="19" t="s">
+      <c r="L23" s="18" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="12" t="s">
         <v>170</v>
       </c>
       <c r="B24" s="9">
@@ -2806,34 +2836,34 @@
       <c r="C24" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H24" s="17" t="s">
+      <c r="F24" s="12"/>
+      <c r="G24" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H24" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="I24" s="17" t="s">
+      <c r="I24" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="J24" s="17" t="s">
+      <c r="J24" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="K24" s="17" t="s">
+      <c r="K24" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="L24" s="19" t="s">
+      <c r="L24" s="18" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="12" t="s">
         <v>174</v>
       </c>
       <c r="B25" s="9">
@@ -2842,34 +2872,34 @@
       <c r="C25" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H25" s="17" t="s">
+      <c r="F25" s="12"/>
+      <c r="G25" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H25" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="I25" s="17" t="s">
+      <c r="I25" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="J25" s="17" t="s">
+      <c r="J25" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="K25" s="17" t="s">
+      <c r="K25" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="L25" s="19" t="s">
+      <c r="L25" s="18" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="12" t="s">
         <v>180</v>
       </c>
       <c r="B26" s="9">
@@ -2878,34 +2908,34 @@
       <c r="C26" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E26" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H26" s="17" t="s">
+      <c r="F26" s="12"/>
+      <c r="G26" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H26" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="I26" s="17" t="s">
+      <c r="I26" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="J26" s="17" t="s">
+      <c r="J26" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="K26" s="17" t="s">
+      <c r="K26" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="L26" s="19" t="s">
+      <c r="L26" s="18" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="12" t="s">
         <v>185</v>
       </c>
       <c r="B27" s="9">
@@ -2914,34 +2944,34 @@
       <c r="C27" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="E27" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H27" s="17" t="s">
+      <c r="F27" s="12"/>
+      <c r="G27" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H27" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="I27" s="17" t="s">
+      <c r="I27" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="J27" s="17" t="s">
+      <c r="J27" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="K27" s="17" t="s">
+      <c r="K27" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="L27" s="19" t="s">
+      <c r="L27" s="18" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="12" t="s">
         <v>189</v>
       </c>
       <c r="B28" s="9">
@@ -2950,34 +2980,34 @@
       <c r="C28" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="E28" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H28" s="17" t="s">
+      <c r="F28" s="12"/>
+      <c r="G28" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H28" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="I28" s="17" t="s">
+      <c r="I28" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="J28" s="17" t="s">
+      <c r="J28" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="K28" s="17" t="s">
+      <c r="K28" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="L28" s="19" t="s">
+      <c r="L28" s="18" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="12" t="s">
         <v>194</v>
       </c>
       <c r="B29" s="9">
@@ -2986,34 +3016,34 @@
       <c r="C29" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="E29" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H29" s="17" t="s">
+      <c r="F29" s="12"/>
+      <c r="G29" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H29" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="I29" s="17" t="s">
+      <c r="I29" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="J29" s="17" t="s">
+      <c r="J29" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="K29" s="17" t="s">
+      <c r="K29" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="L29" s="19" t="s">
+      <c r="L29" s="18" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="12" t="s">
         <v>199</v>
       </c>
       <c r="B30" s="9">
@@ -3022,34 +3052,34 @@
       <c r="C30" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="E30" s="14" t="s">
+      <c r="E30" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H30" s="17" t="s">
+      <c r="F30" s="12"/>
+      <c r="G30" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H30" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="I30" s="17" t="s">
+      <c r="I30" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="J30" s="17" t="s">
+      <c r="J30" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="K30" s="17" t="s">
+      <c r="K30" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="L30" s="19" t="s">
+      <c r="L30" s="18" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="12" t="s">
         <v>204</v>
       </c>
       <c r="B31" s="9">
@@ -3058,34 +3088,34 @@
       <c r="C31" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H31" s="17" t="s">
+      <c r="F31" s="12"/>
+      <c r="G31" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H31" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="I31" s="17" t="s">
+      <c r="I31" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="J31" s="17" t="s">
+      <c r="J31" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="K31" s="17" t="s">
+      <c r="K31" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="L31" s="19" t="s">
+      <c r="L31" s="18" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="12" t="s">
         <v>208</v>
       </c>
       <c r="B32" s="9">
@@ -3094,32 +3124,32 @@
       <c r="C32" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D32" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="E32" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H32" s="17" t="s">
+      <c r="F32" s="12"/>
+      <c r="G32" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H32" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="I32" s="17" t="s">
+      <c r="I32" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="J32" s="17" t="s">
+      <c r="J32" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="K32" s="17"/>
-      <c r="L32" s="19" t="s">
+      <c r="K32" s="15"/>
+      <c r="L32" s="18" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="12" t="s">
         <v>214</v>
       </c>
       <c r="B33" s="9">
@@ -3128,34 +3158,34 @@
       <c r="C33" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E33" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H33" s="17" t="s">
+      <c r="F33" s="12"/>
+      <c r="G33" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H33" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="I33" s="17" t="s">
+      <c r="I33" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="J33" s="17" t="s">
+      <c r="J33" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="K33" s="17">
+      <c r="K33" s="15">
         <v>4</v>
       </c>
-      <c r="L33" s="19" t="s">
+      <c r="L33" s="18" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
+      <c r="A34" s="12" t="s">
         <v>219</v>
       </c>
       <c r="B34" s="9">
@@ -3164,34 +3194,34 @@
       <c r="C34" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="E34" s="14" t="s">
+      <c r="E34" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H34" s="17" t="s">
+      <c r="F34" s="12"/>
+      <c r="G34" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H34" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="I34" s="17" t="s">
+      <c r="I34" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="J34" s="17" t="s">
+      <c r="J34" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="K34" s="17">
+      <c r="K34" s="15">
         <v>6</v>
       </c>
-      <c r="L34" s="19" t="s">
+      <c r="L34" s="18" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="12" t="s">
         <v>224</v>
       </c>
       <c r="B35" s="9">
@@ -3200,34 +3230,34 @@
       <c r="C35" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="E35" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H35" s="17" t="s">
+      <c r="F35" s="12"/>
+      <c r="G35" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H35" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="I35" s="17" t="s">
+      <c r="I35" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="J35" s="17" t="s">
+      <c r="J35" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="K35" s="17" t="s">
-        <v>423</v>
-      </c>
-      <c r="L35" s="19" t="s">
+      <c r="K35" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="L35" s="18" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
+      <c r="A36" s="12" t="s">
         <v>229</v>
       </c>
       <c r="B36" s="9">
@@ -3236,66 +3266,66 @@
       <c r="C36" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="D36" s="14" t="s">
+      <c r="D36" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="E36" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H36" s="17" t="s">
+      <c r="F36" s="12"/>
+      <c r="G36" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H36" s="15" t="s">
         <v>230</v>
       </c>
-      <c r="I36" s="17" t="s">
+      <c r="I36" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="J36" s="17" t="s">
+      <c r="J36" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="K36" s="17"/>
-      <c r="L36" s="19" t="s">
+      <c r="K36" s="15"/>
+      <c r="L36" s="18" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
+      <c r="A37" s="12" t="s">
         <v>234</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="D37" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E37" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H37" s="17" t="s">
+      <c r="F37" s="12"/>
+      <c r="G37" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H37" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="I37" s="17" t="s">
+      <c r="I37" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="J37" s="17" t="s">
+      <c r="J37" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="K37" s="17"/>
-      <c r="L37" s="19" t="s">
+      <c r="K37" s="15"/>
+      <c r="L37" s="18" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
+      <c r="A38" s="12" t="s">
         <v>238</v>
       </c>
       <c r="B38" s="9">
@@ -3304,34 +3334,36 @@
       <c r="C38" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="D38" s="14" t="s">
+      <c r="D38" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="E38" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F38" s="14" t="s">
+      <c r="F38" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="G38" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H38" s="17" t="s">
+      <c r="G38" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H38" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="I38" s="17" t="s">
+      <c r="I38" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="J38" s="17" t="s">
+      <c r="J38" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="K38" s="17"/>
-      <c r="L38" s="19" t="s">
+      <c r="K38" s="15">
+        <v>45</v>
+      </c>
+      <c r="L38" s="18" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="12" t="s">
         <v>245</v>
       </c>
       <c r="B39" s="9">
@@ -3340,34 +3372,36 @@
       <c r="C39" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="D39" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="E39" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F39" s="14" t="s">
+      <c r="F39" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="G39" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H39" s="17" t="s">
+      <c r="G39" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H39" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="I39" s="17" t="s">
+      <c r="I39" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="J39" s="17" t="s">
+      <c r="J39" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="K39" s="17"/>
-      <c r="L39" s="19" t="s">
+      <c r="K39" s="15">
+        <v>61</v>
+      </c>
+      <c r="L39" s="18" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="14" t="s">
+      <c r="A40" s="12" t="s">
         <v>249</v>
       </c>
       <c r="B40" s="9">
@@ -3376,34 +3410,36 @@
       <c r="C40" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="D40" s="14" t="s">
+      <c r="D40" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E40" s="14" t="s">
+      <c r="E40" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F40" s="14" t="s">
+      <c r="F40" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="G40" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H40" s="17" t="s">
+      <c r="G40" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H40" s="15" t="s">
         <v>250</v>
       </c>
-      <c r="I40" s="17" t="s">
+      <c r="I40" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="J40" s="17" t="s">
+      <c r="J40" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="K40" s="17"/>
-      <c r="L40" s="19" t="s">
+      <c r="K40" s="15">
+        <v>57</v>
+      </c>
+      <c r="L40" s="18" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="14" t="s">
+      <c r="A41" s="12" t="s">
         <v>253</v>
       </c>
       <c r="B41" s="9">
@@ -3412,34 +3448,36 @@
       <c r="C41" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="D41" s="14" t="s">
+      <c r="D41" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="E41" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F41" s="14" t="s">
+      <c r="F41" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="G41" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H41" s="17" t="s">
+      <c r="G41" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H41" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="I41" s="17" t="s">
+      <c r="I41" s="15" t="s">
         <v>256</v>
       </c>
-      <c r="J41" s="17" t="s">
+      <c r="J41" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="K41" s="17"/>
-      <c r="L41" s="19" t="s">
+      <c r="K41" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="L41" s="18" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="14" t="s">
+      <c r="A42" s="12" t="s">
         <v>259</v>
       </c>
       <c r="B42" s="9">
@@ -3448,34 +3486,36 @@
       <c r="C42" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="D42" s="14" t="s">
+      <c r="D42" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E42" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F42" s="14" t="s">
+      <c r="F42" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="G42" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H42" s="17" t="s">
+      <c r="G42" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H42" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="I42" s="17" t="s">
+      <c r="I42" s="15" t="s">
         <v>261</v>
       </c>
-      <c r="J42" s="17" t="s">
+      <c r="J42" s="15" t="s">
         <v>262</v>
       </c>
-      <c r="K42" s="17"/>
-      <c r="L42" s="19" t="s">
+      <c r="K42" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="L42" s="18" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="14" t="s">
+      <c r="A43" s="12" t="s">
         <v>263</v>
       </c>
       <c r="B43" s="9">
@@ -3484,34 +3524,36 @@
       <c r="C43" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="D43" s="14" t="s">
+      <c r="D43" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="E43" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F43" s="14" t="s">
+      <c r="F43" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="G43" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H43" s="17" t="s">
+      <c r="G43" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H43" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="I43" s="17" t="s">
+      <c r="I43" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="J43" s="17" t="s">
+      <c r="J43" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="K43" s="17"/>
-      <c r="L43" s="19" t="s">
+      <c r="K43" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="L43" s="18" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="14" t="s">
+      <c r="A44" s="12" t="s">
         <v>267</v>
       </c>
       <c r="B44" s="9">
@@ -3520,34 +3562,36 @@
       <c r="C44" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="D44" s="14" t="s">
+      <c r="D44" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E44" s="14" t="s">
+      <c r="E44" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F44" s="14" t="s">
+      <c r="F44" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="G44" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H44" s="17" t="s">
+      <c r="G44" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H44" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="I44" s="17" t="s">
+      <c r="I44" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="J44" s="17" t="s">
+      <c r="J44" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="K44" s="17"/>
-      <c r="L44" s="19" t="s">
+      <c r="K44" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="L44" s="18" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="14" t="s">
+      <c r="A45" s="12" t="s">
         <v>273</v>
       </c>
       <c r="B45" s="9">
@@ -3556,34 +3600,36 @@
       <c r="C45" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="D45" s="14" t="s">
+      <c r="D45" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="E45" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F45" s="14" t="s">
+      <c r="F45" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="G45" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H45" s="17" t="s">
+      <c r="G45" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H45" s="15" t="s">
         <v>274</v>
       </c>
-      <c r="I45" s="17" t="s">
+      <c r="I45" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="J45" s="17" t="s">
+      <c r="J45" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="K45" s="17"/>
-      <c r="L45" s="19" t="s">
+      <c r="K45" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="L45" s="18" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="14" t="s">
+      <c r="A46" s="12" t="s">
         <v>277</v>
       </c>
       <c r="B46" s="9">
@@ -3592,34 +3638,36 @@
       <c r="C46" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="D46" s="14" t="s">
+      <c r="D46" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E46" s="14" t="s">
+      <c r="E46" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F46" s="14" t="s">
+      <c r="F46" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="G46" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H46" s="17" t="s">
+      <c r="G46" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H46" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="I46" s="17" t="s">
+      <c r="I46" s="15" t="s">
         <v>279</v>
       </c>
-      <c r="J46" s="17" t="s">
+      <c r="J46" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="K46" s="17"/>
-      <c r="L46" s="19" t="s">
+      <c r="K46" s="15" t="s">
+        <v>433</v>
+      </c>
+      <c r="L46" s="18" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
-      <c r="A47" s="14" t="s">
+    <row r="47" spans="1:12" ht="204" x14ac:dyDescent="0.25">
+      <c r="A47" s="12" t="s">
         <v>281</v>
       </c>
       <c r="B47" s="9">
@@ -3628,34 +3676,36 @@
       <c r="C47" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="D47" s="14" t="s">
+      <c r="D47" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E47" s="14" t="s">
+      <c r="E47" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F47" s="14" t="s">
+      <c r="F47" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="G47" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H47" s="17" t="s">
+      <c r="G47" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H47" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="I47" s="17" t="s">
+      <c r="I47" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="J47" s="17" t="s">
+      <c r="J47" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="K47" s="17"/>
-      <c r="L47" s="19" t="s">
+      <c r="K47" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="L47" s="18" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
-      <c r="A48" s="14" t="s">
+      <c r="A48" s="12" t="s">
         <v>287</v>
       </c>
       <c r="B48" s="9">
@@ -3664,34 +3714,34 @@
       <c r="C48" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="D48" s="14" t="s">
+      <c r="D48" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E48" s="14" t="s">
+      <c r="E48" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F48" s="14" t="s">
+      <c r="F48" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="G48" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H48" s="17" t="s">
+      <c r="G48" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H48" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="I48" s="17" t="s">
+      <c r="I48" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="J48" s="17" t="s">
+      <c r="J48" s="15" t="s">
         <v>290</v>
       </c>
-      <c r="K48" s="17"/>
-      <c r="L48" s="19" t="s">
+      <c r="K48" s="15"/>
+      <c r="L48" s="18" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
-      <c r="A49" s="14" t="s">
+      <c r="A49" s="12" t="s">
         <v>291</v>
       </c>
       <c r="B49" s="9">
@@ -3700,34 +3750,36 @@
       <c r="C49" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="D49" s="14" t="s">
+      <c r="D49" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E49" s="14" t="s">
+      <c r="E49" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F49" s="14" t="s">
+      <c r="F49" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="G49" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H49" s="17" t="s">
+      <c r="G49" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H49" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="I49" s="17" t="s">
+      <c r="I49" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="J49" s="17" t="s">
+      <c r="J49" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="K49" s="17"/>
-      <c r="L49" s="19" t="s">
+      <c r="K49" s="15" t="s">
+        <v>435</v>
+      </c>
+      <c r="L49" s="18" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="14" t="s">
+      <c r="A50" s="12" t="s">
         <v>295</v>
       </c>
       <c r="B50" s="9">
@@ -3736,34 +3788,36 @@
       <c r="C50" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="D50" s="14" t="s">
+      <c r="D50" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E50" s="14" t="s">
+      <c r="E50" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F50" s="14" t="s">
+      <c r="F50" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="G50" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H50" s="17" t="s">
+      <c r="G50" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H50" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="I50" s="17" t="s">
+      <c r="I50" s="15" t="s">
         <v>298</v>
       </c>
-      <c r="J50" s="17" t="s">
+      <c r="J50" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="K50" s="17"/>
-      <c r="L50" s="19" t="s">
+      <c r="K50" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="L50" s="18" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="14" t="s">
+      <c r="A51" s="12" t="s">
         <v>301</v>
       </c>
       <c r="B51" s="9">
@@ -3772,34 +3826,36 @@
       <c r="C51" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="D51" s="14" t="s">
+      <c r="D51" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E51" s="14" t="s">
+      <c r="E51" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F51" s="14" t="s">
+      <c r="F51" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="G51" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H51" s="17" t="s">
+      <c r="G51" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H51" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="I51" s="17" t="s">
+      <c r="I51" s="15" t="s">
         <v>303</v>
       </c>
-      <c r="J51" s="17" t="s">
+      <c r="J51" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="K51" s="17"/>
-      <c r="L51" s="19" t="s">
+      <c r="K51" s="15" t="s">
+        <v>423</v>
+      </c>
+      <c r="L51" s="18" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="14" t="s">
+      <c r="A52" s="12" t="s">
         <v>305</v>
       </c>
       <c r="B52" s="9">
@@ -3808,34 +3864,36 @@
       <c r="C52" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="D52" s="14" t="s">
+      <c r="D52" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E52" s="14" t="s">
+      <c r="E52" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F52" s="14" t="s">
+      <c r="F52" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="G52" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H52" s="17" t="s">
+      <c r="G52" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H52" s="15" t="s">
         <v>306</v>
       </c>
-      <c r="I52" s="17" t="s">
+      <c r="I52" s="15" t="s">
         <v>307</v>
       </c>
-      <c r="J52" s="17" t="s">
+      <c r="J52" s="15" t="s">
         <v>308</v>
       </c>
-      <c r="K52" s="17"/>
-      <c r="L52" s="19" t="s">
+      <c r="K52" s="15" t="s">
+        <v>424</v>
+      </c>
+      <c r="L52" s="18" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="14" t="s">
+      <c r="A53" s="12" t="s">
         <v>309</v>
       </c>
       <c r="B53" s="9">
@@ -3844,37 +3902,37 @@
       <c r="C53" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="D53" s="14" t="s">
+      <c r="D53" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E53" s="14" t="s">
+      <c r="E53" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F53" s="14" t="s">
+      <c r="F53" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="G53" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H53" s="17" t="s">
+      <c r="G53" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H53" s="15" t="s">
         <v>311</v>
       </c>
-      <c r="I53" s="17" t="s">
+      <c r="I53" s="15" t="s">
         <v>312</v>
       </c>
-      <c r="J53" s="17" t="s">
+      <c r="J53" s="15" t="s">
         <v>313</v>
       </c>
-      <c r="K53" s="17" t="s">
+      <c r="K53" s="15" t="s">
+        <v>425</v>
+      </c>
+      <c r="L53" s="18" t="s">
         <v>314</v>
       </c>
-      <c r="L53" s="19" t="s">
+    </row>
+    <row r="54" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="12" t="s">
         <v>315</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="14" t="s">
-        <v>316</v>
       </c>
       <c r="B54" s="9">
         <v>2</v>
@@ -3882,37 +3940,37 @@
       <c r="C54" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="D54" s="14" t="s">
+      <c r="D54" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E54" s="14" t="s">
+      <c r="E54" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F54" s="14" t="s">
+      <c r="F54" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="G54" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H54" s="17" t="s">
+      <c r="G54" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H54" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="I54" s="15" t="s">
         <v>317</v>
       </c>
-      <c r="I54" s="17" t="s">
+      <c r="J54" s="15" t="s">
         <v>318</v>
       </c>
-      <c r="J54" s="17" t="s">
+      <c r="K54" s="15" t="s">
+        <v>426</v>
+      </c>
+      <c r="L54" s="18" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="12" t="s">
         <v>319</v>
-      </c>
-      <c r="K54" s="17" t="s">
-        <v>320</v>
-      </c>
-      <c r="L54" s="19" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="14" t="s">
-        <v>321</v>
       </c>
       <c r="B55" s="9">
         <v>2</v>
@@ -3920,668 +3978,668 @@
       <c r="C55" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="D55" s="14" t="s">
+      <c r="D55" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E55" s="14" t="s">
+      <c r="E55" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F55" s="14" t="s">
+      <c r="F55" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="G55" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H55" s="17" t="s">
+      <c r="G55" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H55" s="15" t="s">
+        <v>320</v>
+      </c>
+      <c r="I55" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="J55" s="15" t="s">
         <v>322</v>
       </c>
-      <c r="I55" s="17" t="s">
+      <c r="K55" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="L55" s="18" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A56" s="12" t="s">
         <v>323</v>
-      </c>
-      <c r="J55" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="K55" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="L55" s="19" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A56" s="14" t="s">
-        <v>326</v>
       </c>
       <c r="B56" s="9">
         <v>3</v>
       </c>
       <c r="C56" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H56" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="I56" s="15" t="s">
         <v>327</v>
       </c>
-      <c r="D56" s="14" t="s">
+      <c r="J56" s="15" t="s">
         <v>328</v>
       </c>
-      <c r="E56" s="14" t="s">
-        <v>327</v>
-      </c>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H56" s="17" t="s">
+      <c r="K56" s="15"/>
+      <c r="L56" s="18" t="s">
         <v>329</v>
       </c>
-      <c r="I56" s="17" t="s">
+    </row>
+    <row r="57" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A57" s="12" t="s">
         <v>330</v>
-      </c>
-      <c r="J56" s="17" t="s">
-        <v>331</v>
-      </c>
-      <c r="K56" s="17"/>
-      <c r="L56" s="19" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A57" s="14" t="s">
-        <v>333</v>
       </c>
       <c r="B57" s="9">
         <v>3</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="D57" s="14" t="s">
-        <v>328</v>
-      </c>
-      <c r="E57" s="14" t="s">
-        <v>327</v>
-      </c>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H57" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H57" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="I57" s="15" t="s">
+        <v>332</v>
+      </c>
+      <c r="J57" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="K57" s="15"/>
+      <c r="L57" s="18" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A58" s="12" t="s">
         <v>334</v>
-      </c>
-      <c r="I57" s="17" t="s">
-        <v>335</v>
-      </c>
-      <c r="J57" s="17" t="s">
-        <v>336</v>
-      </c>
-      <c r="K57" s="17"/>
-      <c r="L57" s="19" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A58" s="14" t="s">
-        <v>337</v>
       </c>
       <c r="B58" s="9">
         <v>3</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="D58" s="14" t="s">
-        <v>328</v>
-      </c>
-      <c r="E58" s="14" t="s">
-        <v>327</v>
-      </c>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H58" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="E58" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H58" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="I58" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="J58" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="K58" s="15"/>
+      <c r="L58" s="18" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A59" s="12" t="s">
         <v>338</v>
-      </c>
-      <c r="I58" s="17" t="s">
-        <v>339</v>
-      </c>
-      <c r="J58" s="17" t="s">
-        <v>340</v>
-      </c>
-      <c r="K58" s="17"/>
-      <c r="L58" s="19" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A59" s="14" t="s">
-        <v>341</v>
       </c>
       <c r="B59" s="9">
         <v>3</v>
       </c>
       <c r="C59" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H59" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="I59" s="15" t="s">
         <v>342</v>
       </c>
-      <c r="D59" s="14" t="s">
+      <c r="J59" s="15" t="s">
         <v>343</v>
       </c>
-      <c r="E59" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H59" s="17" t="s">
+      <c r="K59" s="15" t="s">
         <v>344</v>
       </c>
-      <c r="I59" s="17" t="s">
+      <c r="L59" s="18" t="s">
         <v>345</v>
       </c>
-      <c r="J59" s="17" t="s">
+    </row>
+    <row r="60" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A60" s="12" t="s">
         <v>346</v>
-      </c>
-      <c r="K59" s="17" t="s">
-        <v>347</v>
-      </c>
-      <c r="L59" s="19" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A60" s="14" t="s">
-        <v>349</v>
       </c>
       <c r="B60" s="9">
         <v>3</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="D60" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="E60" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H60" s="17" t="s">
+        <v>339</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H60" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="I60" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="J60" s="15" t="s">
+        <v>349</v>
+      </c>
+      <c r="K60" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="L60" s="18" t="s">
         <v>350</v>
       </c>
-      <c r="I60" s="17" t="s">
+    </row>
+    <row r="61" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A61" s="12" t="s">
         <v>351</v>
-      </c>
-      <c r="J60" s="17" t="s">
-        <v>352</v>
-      </c>
-      <c r="K60" s="17" t="s">
-        <v>347</v>
-      </c>
-      <c r="L60" s="19" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="14" t="s">
-        <v>354</v>
       </c>
       <c r="B61" s="9">
         <v>3</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="D61" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="E61" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H61" s="17" t="s">
+        <v>339</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H61" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="I61" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="J61" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="K61" s="16" t="s">
         <v>355</v>
       </c>
-      <c r="I61" s="17" t="s">
+      <c r="L61" s="18" t="s">
         <v>356</v>
       </c>
-      <c r="J61" s="17" t="s">
+    </row>
+    <row r="62" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A62" s="12" t="s">
         <v>357</v>
-      </c>
-      <c r="K61" s="17" t="s">
-        <v>358</v>
-      </c>
-      <c r="L61" s="19" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A62" s="14" t="s">
-        <v>360</v>
       </c>
       <c r="B62" s="9">
         <v>3</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="D62" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="E62" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H62" s="17" t="s">
+        <v>339</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H62" s="15" t="s">
+        <v>358</v>
+      </c>
+      <c r="I62" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="J62" s="15" t="s">
+        <v>360</v>
+      </c>
+      <c r="K62" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="L62" s="18" t="s">
         <v>361</v>
       </c>
-      <c r="I62" s="17" t="s">
+    </row>
+    <row r="63" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+      <c r="A63" s="12" t="s">
         <v>362</v>
-      </c>
-      <c r="J62" s="17" t="s">
-        <v>363</v>
-      </c>
-      <c r="K62" s="17" t="s">
-        <v>358</v>
-      </c>
-      <c r="L62" s="19" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" ht="51" x14ac:dyDescent="0.25">
-      <c r="A63" s="14" t="s">
-        <v>365</v>
       </c>
       <c r="B63" s="9">
         <v>3</v>
       </c>
       <c r="C63" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="F63" s="12"/>
+      <c r="G63" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H63" s="15" t="s">
+        <v>365</v>
+      </c>
+      <c r="I63" s="15" t="s">
         <v>366</v>
       </c>
-      <c r="D63" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="E63" s="14" t="s">
+      <c r="J63" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H63" s="17" t="s">
+      <c r="K63" s="15" t="s">
         <v>368</v>
       </c>
-      <c r="I63" s="17" t="s">
+      <c r="L63" s="18" t="s">
         <v>369</v>
       </c>
-      <c r="J63" s="17" t="s">
+    </row>
+    <row r="64" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+      <c r="A64" s="12" t="s">
         <v>370</v>
-      </c>
-      <c r="K63" s="17" t="s">
-        <v>371</v>
-      </c>
-      <c r="L63" s="19" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" ht="51" x14ac:dyDescent="0.25">
-      <c r="A64" s="14" t="s">
-        <v>373</v>
       </c>
       <c r="B64" s="9">
         <v>3</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="D64" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="E64" s="14" t="s">
-        <v>367</v>
-      </c>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H64" s="17" t="s">
+        <v>363</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H64" s="15" t="s">
+        <v>371</v>
+      </c>
+      <c r="I64" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="J64" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="K64" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="L64" s="18" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+      <c r="A65" s="12" t="s">
         <v>374</v>
-      </c>
-      <c r="I64" s="17" t="s">
-        <v>375</v>
-      </c>
-      <c r="J64" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="K64" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="L64" s="19" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" ht="51" x14ac:dyDescent="0.25">
-      <c r="A65" s="14" t="s">
-        <v>377</v>
       </c>
       <c r="B65" s="9">
         <v>3</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="D65" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="E65" s="14" t="s">
-        <v>367</v>
-      </c>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H65" s="17" t="s">
-        <v>378</v>
-      </c>
-      <c r="I65" s="17" t="s">
-        <v>379</v>
-      </c>
-      <c r="J65" s="17" t="s">
+        <v>363</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="E65" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H65" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="I65" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="J65" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="K65" s="17" t="s">
+      <c r="K65" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="L65" s="19" t="s">
-        <v>372</v>
+      <c r="L65" s="18" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="51" x14ac:dyDescent="0.25">
-      <c r="A66" s="14" t="s">
-        <v>380</v>
+      <c r="A66" s="12" t="s">
+        <v>377</v>
       </c>
       <c r="B66" s="9">
         <v>3</v>
       </c>
       <c r="C66" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="E66" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H66" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="I66" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="J66" s="15" t="s">
+        <v>367</v>
+      </c>
+      <c r="K66" s="15" t="s">
+        <v>368</v>
+      </c>
+      <c r="L66" s="18" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+      <c r="A67" s="12" t="s">
         <v>381</v>
-      </c>
-      <c r="D66" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="E66" s="14" t="s">
-        <v>367</v>
-      </c>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H66" s="17" t="s">
-        <v>382</v>
-      </c>
-      <c r="I66" s="17" t="s">
-        <v>383</v>
-      </c>
-      <c r="J66" s="17" t="s">
-        <v>370</v>
-      </c>
-      <c r="K66" s="17" t="s">
-        <v>371</v>
-      </c>
-      <c r="L66" s="19" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="51" x14ac:dyDescent="0.25">
-      <c r="A67" s="14" t="s">
-        <v>384</v>
       </c>
       <c r="B67" s="9">
         <v>3</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="D67" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="E67" s="14" t="s">
-        <v>367</v>
-      </c>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H67" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H67" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="I67" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="J67" s="15" t="s">
+        <v>384</v>
+      </c>
+      <c r="K67" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="L67" s="18" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+      <c r="A68" s="12" t="s">
         <v>385</v>
-      </c>
-      <c r="I67" s="17" t="s">
-        <v>386</v>
-      </c>
-      <c r="J67" s="17" t="s">
-        <v>387</v>
-      </c>
-      <c r="K67" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="L67" s="19" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="51" x14ac:dyDescent="0.25">
-      <c r="A68" s="14" t="s">
-        <v>388</v>
       </c>
       <c r="B68" s="9">
         <v>3</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="D68" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="E68" s="14" t="s">
-        <v>367</v>
-      </c>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H68" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="E68" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H68" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="I68" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="J68" s="15" t="s">
+        <v>388</v>
+      </c>
+      <c r="K68" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="L68" s="18" t="s">
         <v>389</v>
       </c>
-      <c r="I68" s="17" t="s">
+    </row>
+    <row r="69" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+      <c r="A69" s="12" t="s">
         <v>390</v>
-      </c>
-      <c r="J68" s="17" t="s">
-        <v>391</v>
-      </c>
-      <c r="K68" s="17" t="s">
-        <v>347</v>
-      </c>
-      <c r="L68" s="19" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" ht="51" x14ac:dyDescent="0.25">
-      <c r="A69" s="14" t="s">
-        <v>393</v>
       </c>
       <c r="B69" s="9">
         <v>3</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="D69" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="E69" s="14" t="s">
-        <v>367</v>
-      </c>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H69" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="E69" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H69" s="15" t="s">
+        <v>391</v>
+      </c>
+      <c r="I69" s="15" t="s">
+        <v>392</v>
+      </c>
+      <c r="J69" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="K69" s="15" t="s">
         <v>394</v>
       </c>
-      <c r="I69" s="17" t="s">
+      <c r="L69" s="18" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="229.5" x14ac:dyDescent="0.25">
+      <c r="A70" s="12" t="s">
         <v>395</v>
-      </c>
-      <c r="J69" s="17" t="s">
-        <v>396</v>
-      </c>
-      <c r="K69" s="17" t="s">
-        <v>397</v>
-      </c>
-      <c r="L69" s="19" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="229.5" x14ac:dyDescent="0.25">
-      <c r="A70" s="14" t="s">
-        <v>398</v>
       </c>
       <c r="B70" s="9">
         <v>3</v>
       </c>
       <c r="C70" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="E70" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="F70" s="12"/>
+      <c r="G70" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H70" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="I70" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="J70" s="15" t="s">
         <v>399</v>
       </c>
-      <c r="D70" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="E70" s="14" t="s">
-        <v>367</v>
-      </c>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H70" s="17" t="s">
+      <c r="K70" s="15"/>
+      <c r="L70" s="18" t="s">
         <v>400</v>
       </c>
-      <c r="I70" s="17" t="s">
+    </row>
+    <row r="71" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A71" s="12" t="s">
         <v>401</v>
-      </c>
-      <c r="J70" s="17" t="s">
-        <v>402</v>
-      </c>
-      <c r="K70" s="17"/>
-      <c r="L70" s="19" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
-      <c r="A71" s="14" t="s">
-        <v>404</v>
       </c>
       <c r="B71" s="9">
         <v>3</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>399</v>
-      </c>
-      <c r="D71" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="E71" s="14" t="s">
-        <v>367</v>
-      </c>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H71" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="F71" s="12"/>
+      <c r="G71" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H71" s="15" t="s">
+        <v>402</v>
+      </c>
+      <c r="I71" s="15" t="s">
+        <v>403</v>
+      </c>
+      <c r="J71" s="15" t="s">
+        <v>404</v>
+      </c>
+      <c r="K71" s="15" t="s">
         <v>405</v>
       </c>
-      <c r="I71" s="17" t="s">
+      <c r="L71" s="18" t="s">
         <v>406</v>
       </c>
-      <c r="J71" s="17" t="s">
+    </row>
+    <row r="72" spans="1:12" ht="140.25" x14ac:dyDescent="0.25">
+      <c r="A72" s="12" t="s">
         <v>407</v>
-      </c>
-      <c r="K71" s="17" t="s">
-        <v>408</v>
-      </c>
-      <c r="L71" s="19" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="140.25" x14ac:dyDescent="0.25">
-      <c r="A72" s="14" t="s">
-        <v>410</v>
       </c>
       <c r="B72" s="9">
         <v>3</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>399</v>
-      </c>
-      <c r="D72" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="E72" s="14" t="s">
-        <v>367</v>
-      </c>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H72" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="E72" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="F72" s="12"/>
+      <c r="G72" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H72" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="I72" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="J72" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="K72" s="15"/>
+      <c r="L72" s="18" t="s">
         <v>411</v>
       </c>
-      <c r="I72" s="17" t="s">
+    </row>
+    <row r="73" spans="1:12" ht="127.5" x14ac:dyDescent="0.25">
+      <c r="A73" s="12" t="s">
         <v>412</v>
-      </c>
-      <c r="J72" s="17" t="s">
-        <v>413</v>
-      </c>
-      <c r="K72" s="17"/>
-      <c r="L72" s="19" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="127.5" x14ac:dyDescent="0.25">
-      <c r="A73" s="14" t="s">
-        <v>415</v>
       </c>
       <c r="B73" s="9">
         <v>3</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>399</v>
-      </c>
-      <c r="D73" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="E73" s="14" t="s">
-        <v>367</v>
-      </c>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H73" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="E73" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="F73" s="12"/>
+      <c r="G73" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="H73" s="15" t="s">
+        <v>413</v>
+      </c>
+      <c r="I73" s="15" t="s">
+        <v>414</v>
+      </c>
+      <c r="J73" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="K73" s="15"/>
+      <c r="L73" s="18" t="s">
         <v>416</v>
-      </c>
-      <c r="I73" s="17" t="s">
-        <v>417</v>
-      </c>
-      <c r="J73" s="17" t="s">
-        <v>418</v>
-      </c>
-      <c r="K73" s="17"/>
-      <c r="L73" s="19" t="s">
-        <v>419</v>
       </c>
     </row>
   </sheetData>

--- a/NL2SPARQL_Evaluation_Dataset.xlsx
+++ b/NL2SPARQL_Evaluation_Dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fersi\Desktop\NL2SPARQL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{143BA9D6-44A1-4013-8F0D-EFB2787C32F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D9FE86-09D9-49A9-9DB8-090BB26A652D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="13410" windowHeight="14235" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="26640" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Legend" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="435">
   <si>
     <t>NL2SPARQL Evaluation Dataset — Legend</t>
   </si>
@@ -1287,9 +1287,6 @@
   </si>
   <si>
     <t>AI180</t>
-  </si>
-  <si>
-    <t>1+B36:B37</t>
   </si>
   <si>
     <t>ESB, SOF, SBZ (in that order, highest first)</t>
@@ -1422,7 +1419,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1431,17 +1428,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1470,6 +1456,8 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1780,12 +1768,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -1984,23 +1972,23 @@
   <dimension ref="A1:L73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25" style="13" customWidth="1"/>
-    <col min="2" max="2" width="6" style="10" customWidth="1"/>
-    <col min="3" max="3" width="22" style="13" customWidth="1"/>
-    <col min="4" max="4" width="12" style="13" customWidth="1"/>
-    <col min="5" max="5" width="16" style="13" customWidth="1"/>
-    <col min="6" max="6" width="20" style="13" customWidth="1"/>
-    <col min="7" max="7" width="12" style="13" customWidth="1"/>
-    <col min="8" max="10" width="46" style="13" customWidth="1"/>
-    <col min="11" max="11" width="46.42578125" style="13" customWidth="1"/>
-    <col min="12" max="12" width="30" style="10" customWidth="1"/>
+    <col min="1" max="1" width="25" style="8" customWidth="1"/>
+    <col min="2" max="2" width="6" style="8" customWidth="1"/>
+    <col min="3" max="3" width="22" style="8" customWidth="1"/>
+    <col min="4" max="4" width="12" style="8" customWidth="1"/>
+    <col min="5" max="5" width="16" style="8" customWidth="1"/>
+    <col min="6" max="6" width="20" style="8" customWidth="1"/>
+    <col min="7" max="7" width="12" style="8" customWidth="1"/>
+    <col min="8" max="10" width="46" style="8" customWidth="1"/>
+    <col min="11" max="11" width="46.42578125" style="8" customWidth="1"/>
+    <col min="12" max="12" width="30" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C1" s="4" t="s">
@@ -2035,2610 +2023,2610 @@
       </c>
     </row>
     <row r="2" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="6">
         <v>1</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11" t="s">
+      <c r="F2" s="6"/>
+      <c r="G2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="L2" s="17" t="s">
+      <c r="L2" s="12" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="7">
         <v>1</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12" t="s">
+      <c r="F3" s="7"/>
+      <c r="G3" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="I3" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="J3" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="K3" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="L3" s="18" t="s">
+      <c r="L3" s="13" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="7">
         <v>1</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12" t="s">
+      <c r="F4" s="7"/>
+      <c r="G4" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="J4" s="15" t="s">
+      <c r="J4" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="K4" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="L4" s="18" t="s">
+      <c r="L4" s="13" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="7">
         <v>1</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12" t="s">
+      <c r="F5" s="7"/>
+      <c r="G5" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="K5" s="15">
+      <c r="K5" s="10">
         <v>400</v>
       </c>
-      <c r="L5" s="18" t="s">
+      <c r="L5" s="13" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="7">
         <v>1</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12" t="s">
+      <c r="F6" s="7"/>
+      <c r="G6" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="K6" s="15" t="s">
+      <c r="K6" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="L6" s="18" t="s">
+      <c r="L6" s="13" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="7">
         <v>1</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12" t="s">
+      <c r="F7" s="7"/>
+      <c r="G7" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="I7" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="J7" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="K7" s="15" t="s">
+      <c r="K7" s="10" t="s">
         <v>417</v>
       </c>
-      <c r="L7" s="18" t="s">
+      <c r="L7" s="13" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="7">
         <v>1</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12" t="s">
+      <c r="F8" s="7"/>
+      <c r="G8" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I8" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="J8" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="K8" s="15" t="s">
+      <c r="K8" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="L8" s="18" t="s">
+      <c r="L8" s="13" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="7">
         <v>1</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12" t="s">
+      <c r="F9" s="7"/>
+      <c r="G9" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="I9" s="15" t="s">
+      <c r="I9" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="J9" s="15" t="s">
+      <c r="J9" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="K9" s="15" t="s">
+      <c r="K9" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="L9" s="18" t="s">
+      <c r="L9" s="13" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="7">
         <v>1</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12" t="s">
+      <c r="F10" s="7"/>
+      <c r="G10" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="H10" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="I10" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="J10" s="15" t="s">
+      <c r="J10" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="K10" s="15" t="s">
+      <c r="K10" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="L10" s="18" t="s">
+      <c r="L10" s="13" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="6">
         <v>1</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11" t="s">
+      <c r="F11" s="6"/>
+      <c r="G11" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H11" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="J11" s="14" t="s">
+      <c r="J11" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="K11" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="L11" s="17" t="s">
+      <c r="L11" s="12" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="7">
         <v>1</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12" t="s">
+      <c r="F12" s="7"/>
+      <c r="G12" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H12" s="15" t="s">
+      <c r="H12" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="I12" s="15" t="s">
+      <c r="I12" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="J12" s="15" t="s">
+      <c r="J12" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="K12" s="15" t="s">
+      <c r="K12" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="L12" s="18" t="s">
+      <c r="L12" s="13" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="7">
         <v>1</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12" t="s">
+      <c r="F13" s="7"/>
+      <c r="G13" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H13" s="15" t="s">
+      <c r="H13" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="I13" s="15" t="s">
+      <c r="I13" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="J13" s="15" t="s">
+      <c r="J13" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="K13" s="15" t="s">
+      <c r="K13" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="L13" s="18" t="s">
+      <c r="L13" s="13" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="7">
         <v>1</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12" t="s">
+      <c r="F14" s="7"/>
+      <c r="G14" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="H14" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="I14" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="J14" s="15" t="s">
+      <c r="J14" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="K14" s="15" t="s">
+      <c r="K14" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="L14" s="18" t="s">
+      <c r="L14" s="13" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="7">
         <v>1</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12" t="s">
+      <c r="F15" s="7"/>
+      <c r="G15" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="15" t="s">
+      <c r="H15" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="I15" s="15" t="s">
+      <c r="I15" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="J15" s="15" t="s">
+      <c r="J15" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="K15" s="15" t="s">
+      <c r="K15" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="L15" s="18" t="s">
+      <c r="L15" s="13" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="51" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="7">
         <v>1</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12" t="s">
+      <c r="F16" s="7"/>
+      <c r="G16" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H16" s="15" t="s">
+      <c r="H16" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="I16" s="15" t="s">
+      <c r="I16" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="J16" s="15" t="s">
+      <c r="J16" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="K16" s="15" t="s">
+      <c r="K16" s="10" t="s">
         <v>418</v>
       </c>
-      <c r="L16" s="18" t="s">
+      <c r="L16" s="13" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="7">
         <v>1</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12" t="s">
+      <c r="F17" s="7"/>
+      <c r="G17" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H17" s="15" t="s">
+      <c r="H17" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="I17" s="15" t="s">
+      <c r="I17" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="J17" s="15" t="s">
+      <c r="J17" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="K17" s="15" t="s">
+      <c r="K17" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="L17" s="18" t="s">
+      <c r="L17" s="13" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="7">
         <v>1</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12" t="s">
+      <c r="F18" s="7"/>
+      <c r="G18" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H18" s="15" t="s">
+      <c r="H18" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="I18" s="15" t="s">
+      <c r="I18" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="J18" s="15" t="s">
+      <c r="J18" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="K18" s="15" t="s">
+      <c r="K18" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="L18" s="18" t="s">
+      <c r="L18" s="13" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="7">
         <v>1</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12" t="s">
+      <c r="F19" s="7"/>
+      <c r="G19" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H19" s="15" t="s">
+      <c r="H19" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="I19" s="15" t="s">
+      <c r="I19" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="J19" s="15" t="s">
+      <c r="J19" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="K19" s="15" t="s">
+      <c r="K19" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="L19" s="18" t="s">
+      <c r="L19" s="13" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="6">
         <v>1</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="H20" s="14" t="s">
+      <c r="F20" s="6"/>
+      <c r="G20" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="H20" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="I20" s="14" t="s">
+      <c r="I20" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="J20" s="14" t="s">
+      <c r="J20" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="K20" s="14" t="s">
+      <c r="K20" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="L20" s="17" t="s">
+      <c r="L20" s="12" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B21" s="7">
         <v>1</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H21" s="15" t="s">
+      <c r="F21" s="7"/>
+      <c r="G21" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H21" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="I21" s="15" t="s">
+      <c r="I21" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="J21" s="15" t="s">
+      <c r="J21" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="K21" s="15" t="s">
+      <c r="K21" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="L21" s="18" t="s">
+      <c r="L21" s="13" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B22" s="7">
         <v>1</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E22" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H22" s="15" t="s">
+      <c r="F22" s="7"/>
+      <c r="G22" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H22" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="I22" s="15" t="s">
+      <c r="I22" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="J22" s="15" t="s">
+      <c r="J22" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="K22" s="15" t="s">
+      <c r="K22" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="L22" s="18" t="s">
+      <c r="L22" s="13" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="7">
         <v>1</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="E23" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H23" s="15" t="s">
+      <c r="F23" s="7"/>
+      <c r="G23" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="I23" s="15" t="s">
+      <c r="I23" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="J23" s="15" t="s">
+      <c r="J23" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="K23" s="15" t="s">
+      <c r="K23" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="L23" s="18" t="s">
+      <c r="L23" s="13" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B24" s="7">
         <v>1</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="E24" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H24" s="15" t="s">
+      <c r="F24" s="7"/>
+      <c r="G24" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H24" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="I24" s="15" t="s">
+      <c r="I24" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="J24" s="15" t="s">
+      <c r="J24" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="K24" s="15" t="s">
+      <c r="K24" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="L24" s="18" t="s">
+      <c r="L24" s="13" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="B25" s="9">
+      <c r="B25" s="7">
         <v>1</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E25" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H25" s="15" t="s">
+      <c r="F25" s="7"/>
+      <c r="G25" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="I25" s="15" t="s">
+      <c r="I25" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="J25" s="15" t="s">
+      <c r="J25" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="K25" s="15" t="s">
+      <c r="K25" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="L25" s="18" t="s">
+      <c r="L25" s="13" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="B26" s="9">
+      <c r="B26" s="7">
         <v>1</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H26" s="15" t="s">
+      <c r="F26" s="7"/>
+      <c r="G26" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H26" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="I26" s="15" t="s">
+      <c r="I26" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="J26" s="15" t="s">
+      <c r="J26" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="K26" s="15" t="s">
+      <c r="K26" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="L26" s="18" t="s">
+      <c r="L26" s="13" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="B27" s="9">
+      <c r="B27" s="7">
         <v>1</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="E27" s="12" t="s">
+      <c r="E27" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H27" s="15" t="s">
+      <c r="F27" s="7"/>
+      <c r="G27" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="I27" s="15" t="s">
+      <c r="I27" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="J27" s="15" t="s">
+      <c r="J27" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="K27" s="15" t="s">
+      <c r="K27" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="L27" s="18" t="s">
+      <c r="L27" s="13" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="B28" s="9">
+      <c r="B28" s="7">
         <v>1</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="E28" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H28" s="15" t="s">
+      <c r="F28" s="7"/>
+      <c r="G28" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H28" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="I28" s="15" t="s">
+      <c r="I28" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="J28" s="15" t="s">
+      <c r="J28" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="K28" s="15" t="s">
+      <c r="K28" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="L28" s="18" t="s">
+      <c r="L28" s="13" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="7">
         <v>1</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="E29" s="12" t="s">
+      <c r="E29" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H29" s="15" t="s">
+      <c r="F29" s="7"/>
+      <c r="G29" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="I29" s="15" t="s">
+      <c r="I29" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="J29" s="15" t="s">
+      <c r="J29" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="K29" s="15" t="s">
+      <c r="K29" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="L29" s="18" t="s">
+      <c r="L29" s="13" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B30" s="7">
         <v>1</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="E30" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H30" s="15" t="s">
+      <c r="F30" s="7"/>
+      <c r="G30" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H30" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="I30" s="15" t="s">
+      <c r="I30" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="J30" s="15" t="s">
+      <c r="J30" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="K30" s="15" t="s">
+      <c r="K30" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="L30" s="18" t="s">
+      <c r="L30" s="13" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B31" s="7">
         <v>1</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="E31" s="12" t="s">
+      <c r="E31" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H31" s="15" t="s">
+      <c r="F31" s="7"/>
+      <c r="G31" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="I31" s="15" t="s">
+      <c r="I31" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="J31" s="15" t="s">
+      <c r="J31" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="K31" s="15" t="s">
+      <c r="K31" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="L31" s="18" t="s">
+      <c r="L31" s="13" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32" s="7">
         <v>1</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="E32" s="12" t="s">
+      <c r="E32" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H32" s="15" t="s">
+      <c r="F32" s="7"/>
+      <c r="G32" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H32" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="I32" s="15" t="s">
+      <c r="I32" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="J32" s="15" t="s">
+      <c r="J32" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="K32" s="15"/>
-      <c r="L32" s="18" t="s">
+      <c r="K32" s="10"/>
+      <c r="L32" s="13" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
+      <c r="A33" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="B33" s="9">
+      <c r="B33" s="7">
         <v>1</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="E33" s="12" t="s">
+      <c r="E33" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H33" s="15" t="s">
+      <c r="F33" s="7"/>
+      <c r="G33" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="I33" s="15" t="s">
+      <c r="I33" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="J33" s="15" t="s">
+      <c r="J33" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="K33" s="15">
+      <c r="K33" s="10">
         <v>4</v>
       </c>
-      <c r="L33" s="18" t="s">
+      <c r="L33" s="13" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="s">
+      <c r="A34" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="B34" s="9">
+      <c r="B34" s="7">
         <v>1</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="E34" s="12" t="s">
+      <c r="E34" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H34" s="15" t="s">
+      <c r="F34" s="7"/>
+      <c r="G34" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H34" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="I34" s="15" t="s">
+      <c r="I34" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="J34" s="15" t="s">
+      <c r="J34" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="K34" s="15">
+      <c r="K34" s="10">
         <v>6</v>
       </c>
-      <c r="L34" s="18" t="s">
+      <c r="L34" s="13" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
+      <c r="A35" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="B35" s="9">
+      <c r="B35" s="7">
         <v>1</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="E35" s="12" t="s">
+      <c r="E35" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H35" s="15" t="s">
+      <c r="F35" s="7"/>
+      <c r="G35" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="I35" s="15" t="s">
+      <c r="I35" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="J35" s="15" t="s">
+      <c r="J35" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="K35" s="15" t="s">
+      <c r="K35" s="10" t="s">
         <v>420</v>
       </c>
-      <c r="L35" s="18" t="s">
+      <c r="L35" s="13" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
+      <c r="A36" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="B36" s="9">
+      <c r="B36" s="7">
         <v>1</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="E36" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H36" s="15" t="s">
+      <c r="F36" s="7"/>
+      <c r="G36" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H36" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="I36" s="15" t="s">
+      <c r="I36" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="J36" s="15" t="s">
+      <c r="J36" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="K36" s="15"/>
-      <c r="L36" s="18" t="s">
+      <c r="K36" s="10"/>
+      <c r="L36" s="13" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="7">
+        <v>1</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="K37" s="10"/>
+      <c r="L37" s="13" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B38" s="7">
+        <v>2</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H38" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="K38" s="10">
+        <v>45</v>
+      </c>
+      <c r="L38" s="13" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="B39" s="7">
+        <v>2</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="K39" s="10">
+        <v>61</v>
+      </c>
+      <c r="L39" s="13" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="B40" s="7">
+        <v>2</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="J40" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="K40" s="10">
+        <v>57</v>
+      </c>
+      <c r="L40" s="13" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="B41" s="7">
+        <v>2</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="J41" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="K41" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="L41" s="13" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="B42" s="7">
+        <v>2</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="J42" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="K42" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="L42" s="13" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="B43" s="7">
+        <v>2</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="J43" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="K43" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="L43" s="13" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="B44" s="7">
+        <v>2</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H44" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="I44" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="J44" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="K44" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="L44" s="13" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="B45" s="7">
+        <v>2</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="J45" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="K45" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="L45" s="13" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="B46" s="7">
+        <v>2</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H46" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="J46" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="K46" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="L46" s="13" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A47" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="B47" s="7">
+        <v>2</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="J47" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="K47" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="L47" s="13" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A48" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="B48" s="7">
+        <v>2</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="J48" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="K48" s="10"/>
+      <c r="L48" s="13" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A49" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="B49" s="7">
+        <v>2</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="I49" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="J49" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="K49" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="L49" s="13" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A50" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="B50" s="7">
+        <v>2</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H50" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="I50" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="J50" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="K50" s="10" t="s">
         <v>421</v>
       </c>
-      <c r="C37" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="E37" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H37" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="I37" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="J37" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="K37" s="15"/>
-      <c r="L37" s="18" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="B38" s="9">
+      <c r="L50" s="13" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A51" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="B51" s="7">
         <v>2</v>
       </c>
-      <c r="C38" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="E38" s="12" t="s">
+      <c r="C51" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E51" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="F38" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="G38" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H38" s="15" t="s">
-        <v>241</v>
-      </c>
-      <c r="I38" s="15" t="s">
-        <v>242</v>
-      </c>
-      <c r="J38" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="K38" s="15">
-        <v>45</v>
-      </c>
-      <c r="L38" s="18" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="B39" s="9">
+      <c r="F51" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="I51" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="J51" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="K51" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="L51" s="13" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A52" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="B52" s="7">
         <v>2</v>
       </c>
-      <c r="C39" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="E39" s="12" t="s">
+      <c r="C52" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E52" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="F39" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="G39" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H39" s="15" t="s">
-        <v>246</v>
-      </c>
-      <c r="I39" s="15" t="s">
-        <v>247</v>
-      </c>
-      <c r="J39" s="15" t="s">
-        <v>248</v>
-      </c>
-      <c r="K39" s="15">
-        <v>61</v>
-      </c>
-      <c r="L39" s="18" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="B40" s="9">
+      <c r="F52" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H52" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="I52" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="J52" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="K52" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="L52" s="13" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="B53" s="7">
         <v>2</v>
       </c>
-      <c r="C40" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="E40" s="12" t="s">
+      <c r="C53" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E53" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="F40" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="G40" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H40" s="15" t="s">
-        <v>250</v>
-      </c>
-      <c r="I40" s="15" t="s">
-        <v>251</v>
-      </c>
-      <c r="J40" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="K40" s="15">
-        <v>57</v>
-      </c>
-      <c r="L40" s="18" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
-        <v>253</v>
-      </c>
-      <c r="B41" s="9">
+      <c r="F53" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="I53" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="J53" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="K53" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="L53" s="13" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="B54" s="7">
         <v>2</v>
       </c>
-      <c r="C41" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="E41" s="12" t="s">
+      <c r="C54" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E54" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="F41" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="G41" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H41" s="15" t="s">
-        <v>255</v>
-      </c>
-      <c r="I41" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="J41" s="15" t="s">
-        <v>257</v>
-      </c>
-      <c r="K41" s="15" t="s">
-        <v>428</v>
-      </c>
-      <c r="L41" s="18" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="B42" s="9">
+      <c r="F54" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H54" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="I54" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="J54" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="K54" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="L54" s="13" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="B55" s="7">
         <v>2</v>
       </c>
-      <c r="C42" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="E42" s="12" t="s">
+      <c r="C55" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E55" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="F42" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="G42" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H42" s="15" t="s">
-        <v>260</v>
-      </c>
-      <c r="I42" s="15" t="s">
-        <v>261</v>
-      </c>
-      <c r="J42" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="K42" s="15" t="s">
-        <v>429</v>
-      </c>
-      <c r="L42" s="18" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="12" t="s">
-        <v>263</v>
-      </c>
-      <c r="B43" s="9">
-        <v>2</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="D43" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="E43" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="F43" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="G43" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H43" s="15" t="s">
-        <v>264</v>
-      </c>
-      <c r="I43" s="15" t="s">
-        <v>265</v>
-      </c>
-      <c r="J43" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="K43" s="15" t="s">
-        <v>430</v>
-      </c>
-      <c r="L43" s="18" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="12" t="s">
-        <v>267</v>
-      </c>
-      <c r="B44" s="9">
-        <v>2</v>
-      </c>
-      <c r="C44" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E44" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="F44" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="G44" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H44" s="15" t="s">
-        <v>269</v>
-      </c>
-      <c r="I44" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="J44" s="15" t="s">
-        <v>271</v>
-      </c>
-      <c r="K44" s="15" t="s">
-        <v>431</v>
-      </c>
-      <c r="L44" s="18" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="B45" s="9">
-        <v>2</v>
-      </c>
-      <c r="C45" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E45" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="F45" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="G45" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H45" s="15" t="s">
-        <v>274</v>
-      </c>
-      <c r="I45" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="J45" s="15" t="s">
-        <v>276</v>
-      </c>
-      <c r="K45" s="15" t="s">
-        <v>432</v>
-      </c>
-      <c r="L45" s="18" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="12" t="s">
-        <v>277</v>
-      </c>
-      <c r="B46" s="9">
-        <v>2</v>
-      </c>
-      <c r="C46" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E46" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="F46" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="G46" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H46" s="15" t="s">
-        <v>278</v>
-      </c>
-      <c r="I46" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="J46" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="K46" s="15" t="s">
-        <v>433</v>
-      </c>
-      <c r="L46" s="18" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="204" x14ac:dyDescent="0.25">
-      <c r="A47" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="B47" s="9">
-        <v>2</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E47" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="F47" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="G47" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H47" s="15" t="s">
-        <v>283</v>
-      </c>
-      <c r="I47" s="15" t="s">
-        <v>284</v>
-      </c>
-      <c r="J47" s="15" t="s">
-        <v>285</v>
-      </c>
-      <c r="K47" s="15" t="s">
-        <v>434</v>
-      </c>
-      <c r="L47" s="18" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
-      <c r="A48" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="B48" s="9">
-        <v>2</v>
-      </c>
-      <c r="C48" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E48" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="F48" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="G48" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H48" s="15" t="s">
-        <v>288</v>
-      </c>
-      <c r="I48" s="15" t="s">
-        <v>289</v>
-      </c>
-      <c r="J48" s="15" t="s">
-        <v>290</v>
-      </c>
-      <c r="K48" s="15"/>
-      <c r="L48" s="18" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
-      <c r="A49" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="B49" s="9">
-        <v>2</v>
-      </c>
-      <c r="C49" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E49" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="F49" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="G49" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H49" s="15" t="s">
-        <v>292</v>
-      </c>
-      <c r="I49" s="15" t="s">
-        <v>293</v>
-      </c>
-      <c r="J49" s="15" t="s">
-        <v>294</v>
-      </c>
-      <c r="K49" s="15" t="s">
-        <v>435</v>
-      </c>
-      <c r="L49" s="18" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="B50" s="9">
-        <v>2</v>
-      </c>
-      <c r="C50" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E50" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="F50" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="G50" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H50" s="15" t="s">
-        <v>297</v>
-      </c>
-      <c r="I50" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="J50" s="15" t="s">
-        <v>299</v>
-      </c>
-      <c r="K50" s="15" t="s">
-        <v>422</v>
-      </c>
-      <c r="L50" s="18" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="B51" s="9">
-        <v>2</v>
-      </c>
-      <c r="C51" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E51" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="F51" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="G51" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H51" s="15" t="s">
-        <v>302</v>
-      </c>
-      <c r="I51" s="15" t="s">
-        <v>303</v>
-      </c>
-      <c r="J51" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="K51" s="15" t="s">
-        <v>423</v>
-      </c>
-      <c r="L51" s="18" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="B52" s="9">
-        <v>2</v>
-      </c>
-      <c r="C52" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E52" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="F52" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="G52" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H52" s="15" t="s">
-        <v>306</v>
-      </c>
-      <c r="I52" s="15" t="s">
-        <v>307</v>
-      </c>
-      <c r="J52" s="15" t="s">
-        <v>308</v>
-      </c>
-      <c r="K52" s="15" t="s">
-        <v>424</v>
-      </c>
-      <c r="L52" s="18" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="12" t="s">
-        <v>309</v>
-      </c>
-      <c r="B53" s="9">
-        <v>2</v>
-      </c>
-      <c r="C53" s="12" t="s">
+      <c r="F55" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="D53" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E53" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="F53" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="G53" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H53" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="I53" s="15" t="s">
-        <v>312</v>
-      </c>
-      <c r="J53" s="15" t="s">
-        <v>313</v>
-      </c>
-      <c r="K53" s="15" t="s">
-        <v>425</v>
-      </c>
-      <c r="L53" s="18" t="s">
+      <c r="G55" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H55" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="I55" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="J55" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="K55" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="L55" s="13" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="B54" s="9">
-        <v>2</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E54" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="F54" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="G54" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H54" s="15" t="s">
-        <v>316</v>
-      </c>
-      <c r="I54" s="15" t="s">
-        <v>317</v>
-      </c>
-      <c r="J54" s="15" t="s">
-        <v>318</v>
-      </c>
-      <c r="K54" s="15" t="s">
-        <v>426</v>
-      </c>
-      <c r="L54" s="18" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="B55" s="9">
-        <v>2</v>
-      </c>
-      <c r="C55" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="D55" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E55" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="F55" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="G55" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H55" s="15" t="s">
-        <v>320</v>
-      </c>
-      <c r="I55" s="15" t="s">
-        <v>321</v>
-      </c>
-      <c r="J55" s="15" t="s">
-        <v>322</v>
-      </c>
-      <c r="K55" s="15" t="s">
-        <v>427</v>
-      </c>
-      <c r="L55" s="18" t="s">
-        <v>314</v>
-      </c>
-    </row>
     <row r="56" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A56" s="12" t="s">
+      <c r="A56" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="B56" s="9">
+      <c r="B56" s="7">
         <v>3</v>
       </c>
-      <c r="C56" s="12" t="s">
+      <c r="C56" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="D56" s="12" t="s">
+      <c r="D56" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="E56" s="12" t="s">
+      <c r="E56" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H56" s="15" t="s">
+      <c r="F56" s="7"/>
+      <c r="G56" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H56" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="I56" s="15" t="s">
+      <c r="I56" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="J56" s="15" t="s">
+      <c r="J56" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="K56" s="15"/>
-      <c r="L56" s="18" t="s">
+      <c r="K56" s="10"/>
+      <c r="L56" s="13" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A57" s="12" t="s">
+      <c r="A57" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="B57" s="9">
+      <c r="B57" s="7">
         <v>3</v>
       </c>
-      <c r="C57" s="12" t="s">
+      <c r="C57" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="D57" s="12" t="s">
+      <c r="D57" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="E57" s="12" t="s">
+      <c r="E57" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H57" s="15" t="s">
+      <c r="F57" s="7"/>
+      <c r="G57" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="I57" s="15" t="s">
+      <c r="I57" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="J57" s="15" t="s">
+      <c r="J57" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="K57" s="15"/>
-      <c r="L57" s="18" t="s">
+      <c r="K57" s="10"/>
+      <c r="L57" s="13" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A58" s="12" t="s">
+      <c r="A58" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="B58" s="9">
+      <c r="B58" s="7">
         <v>3</v>
       </c>
-      <c r="C58" s="12" t="s">
+      <c r="C58" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="D58" s="12" t="s">
+      <c r="D58" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="E58" s="12" t="s">
+      <c r="E58" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H58" s="15" t="s">
+      <c r="F58" s="7"/>
+      <c r="G58" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H58" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="I58" s="15" t="s">
+      <c r="I58" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="J58" s="15" t="s">
+      <c r="J58" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="K58" s="15"/>
-      <c r="L58" s="18" t="s">
+      <c r="K58" s="10"/>
+      <c r="L58" s="13" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A59" s="12" t="s">
+      <c r="A59" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="B59" s="9">
+      <c r="B59" s="7">
         <v>3</v>
       </c>
-      <c r="C59" s="12" t="s">
+      <c r="C59" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="D59" s="12" t="s">
+      <c r="D59" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="E59" s="12" t="s">
+      <c r="E59" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="F59" s="12"/>
-      <c r="G59" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H59" s="15" t="s">
+      <c r="F59" s="7"/>
+      <c r="G59" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>341</v>
       </c>
-      <c r="I59" s="15" t="s">
+      <c r="I59" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="J59" s="15" t="s">
+      <c r="J59" s="10" t="s">
         <v>343</v>
       </c>
-      <c r="K59" s="15" t="s">
+      <c r="K59" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="L59" s="18" t="s">
+      <c r="L59" s="13" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A60" s="12" t="s">
+      <c r="A60" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="B60" s="9">
+      <c r="B60" s="7">
         <v>3</v>
       </c>
-      <c r="C60" s="12" t="s">
+      <c r="C60" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="D60" s="12" t="s">
+      <c r="D60" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="E60" s="12" t="s">
+      <c r="E60" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="F60" s="12"/>
-      <c r="G60" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H60" s="15" t="s">
+      <c r="F60" s="7"/>
+      <c r="G60" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H60" s="10" t="s">
         <v>347</v>
       </c>
-      <c r="I60" s="15" t="s">
+      <c r="I60" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="J60" s="15" t="s">
+      <c r="J60" s="10" t="s">
         <v>349</v>
       </c>
-      <c r="K60" s="15" t="s">
+      <c r="K60" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="L60" s="18" t="s">
+      <c r="L60" s="13" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="12" t="s">
+      <c r="A61" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="B61" s="9">
+      <c r="B61" s="7">
         <v>3</v>
       </c>
-      <c r="C61" s="12" t="s">
+      <c r="C61" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="D61" s="12" t="s">
+      <c r="D61" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="E61" s="12" t="s">
+      <c r="E61" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="F61" s="12"/>
-      <c r="G61" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H61" s="15" t="s">
+      <c r="F61" s="7"/>
+      <c r="G61" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>352</v>
       </c>
-      <c r="I61" s="15" t="s">
+      <c r="I61" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="J61" s="15" t="s">
+      <c r="J61" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="K61" s="16" t="s">
+      <c r="K61" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="L61" s="18" t="s">
+      <c r="L61" s="13" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A62" s="12" t="s">
+      <c r="A62" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="B62" s="9">
+      <c r="B62" s="7">
         <v>3</v>
       </c>
-      <c r="C62" s="12" t="s">
+      <c r="C62" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="D62" s="12" t="s">
+      <c r="D62" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="E62" s="12" t="s">
+      <c r="E62" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="F62" s="12"/>
-      <c r="G62" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H62" s="15" t="s">
+      <c r="F62" s="7"/>
+      <c r="G62" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H62" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="I62" s="15" t="s">
+      <c r="I62" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="J62" s="15" t="s">
+      <c r="J62" s="10" t="s">
         <v>360</v>
       </c>
-      <c r="K62" s="15" t="s">
+      <c r="K62" s="10" t="s">
         <v>355</v>
       </c>
-      <c r="L62" s="18" t="s">
+      <c r="L62" s="13" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="51" x14ac:dyDescent="0.25">
-      <c r="A63" s="12" t="s">
+      <c r="A63" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="B63" s="9">
+      <c r="B63" s="7">
         <v>3</v>
       </c>
-      <c r="C63" s="12" t="s">
+      <c r="C63" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="D63" s="12" t="s">
+      <c r="D63" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="E63" s="12" t="s">
+      <c r="E63" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="F63" s="12"/>
-      <c r="G63" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H63" s="15" t="s">
+      <c r="F63" s="7"/>
+      <c r="G63" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>365</v>
       </c>
-      <c r="I63" s="15" t="s">
+      <c r="I63" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="J63" s="15" t="s">
+      <c r="J63" s="10" t="s">
         <v>367</v>
       </c>
-      <c r="K63" s="15" t="s">
+      <c r="K63" s="10" t="s">
         <v>368</v>
       </c>
-      <c r="L63" s="18" t="s">
+      <c r="L63" s="13" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="51" x14ac:dyDescent="0.25">
-      <c r="A64" s="12" t="s">
+      <c r="A64" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="B64" s="9">
+      <c r="B64" s="7">
         <v>3</v>
       </c>
-      <c r="C64" s="12" t="s">
+      <c r="C64" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="D64" s="12" t="s">
+      <c r="D64" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="E64" s="12" t="s">
+      <c r="E64" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="F64" s="12"/>
-      <c r="G64" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H64" s="15" t="s">
+      <c r="F64" s="7"/>
+      <c r="G64" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H64" s="10" t="s">
         <v>371</v>
       </c>
-      <c r="I64" s="15" t="s">
+      <c r="I64" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="J64" s="15" t="s">
+      <c r="J64" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="K64" s="15" t="s">
+      <c r="K64" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="L64" s="18" t="s">
+      <c r="L64" s="13" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="51" x14ac:dyDescent="0.25">
-      <c r="A65" s="12" t="s">
+      <c r="A65" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="B65" s="9">
+      <c r="B65" s="7">
         <v>3</v>
       </c>
-      <c r="C65" s="12" t="s">
+      <c r="C65" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="D65" s="12" t="s">
+      <c r="D65" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="E65" s="12" t="s">
+      <c r="E65" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="F65" s="12"/>
-      <c r="G65" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H65" s="15" t="s">
+      <c r="F65" s="7"/>
+      <c r="G65" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>375</v>
       </c>
-      <c r="I65" s="15" t="s">
+      <c r="I65" s="10" t="s">
         <v>376</v>
       </c>
-      <c r="J65" s="15" t="s">
+      <c r="J65" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="K65" s="15" t="s">
+      <c r="K65" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="L65" s="18" t="s">
+      <c r="L65" s="13" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="51" x14ac:dyDescent="0.25">
-      <c r="A66" s="12" t="s">
+      <c r="A66" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="B66" s="9">
+      <c r="B66" s="7">
         <v>3</v>
       </c>
-      <c r="C66" s="12" t="s">
+      <c r="C66" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="D66" s="12" t="s">
+      <c r="D66" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="E66" s="12" t="s">
+      <c r="E66" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="F66" s="12"/>
-      <c r="G66" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H66" s="15" t="s">
+      <c r="F66" s="7"/>
+      <c r="G66" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H66" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="I66" s="15" t="s">
+      <c r="I66" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="J66" s="15" t="s">
+      <c r="J66" s="10" t="s">
         <v>367</v>
       </c>
-      <c r="K66" s="15" t="s">
+      <c r="K66" s="10" t="s">
         <v>368</v>
       </c>
-      <c r="L66" s="18" t="s">
+      <c r="L66" s="13" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="51" x14ac:dyDescent="0.25">
-      <c r="A67" s="12" t="s">
+      <c r="A67" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="B67" s="9">
+      <c r="B67" s="7">
         <v>3</v>
       </c>
-      <c r="C67" s="12" t="s">
+      <c r="C67" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="D67" s="12" t="s">
+      <c r="D67" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="E67" s="12" t="s">
+      <c r="E67" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="F67" s="12"/>
-      <c r="G67" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H67" s="15" t="s">
+      <c r="F67" s="7"/>
+      <c r="G67" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>382</v>
       </c>
-      <c r="I67" s="15" t="s">
+      <c r="I67" s="10" t="s">
         <v>383</v>
       </c>
-      <c r="J67" s="15" t="s">
+      <c r="J67" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="K67" s="15" t="s">
+      <c r="K67" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="L67" s="18" t="s">
+      <c r="L67" s="13" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="51" x14ac:dyDescent="0.25">
-      <c r="A68" s="12" t="s">
+      <c r="A68" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="B68" s="9">
+      <c r="B68" s="7">
         <v>3</v>
       </c>
-      <c r="C68" s="12" t="s">
+      <c r="C68" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="D68" s="12" t="s">
+      <c r="D68" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="E68" s="12" t="s">
+      <c r="E68" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="F68" s="12"/>
-      <c r="G68" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H68" s="15" t="s">
+      <c r="F68" s="7"/>
+      <c r="G68" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H68" s="10" t="s">
         <v>386</v>
       </c>
-      <c r="I68" s="15" t="s">
+      <c r="I68" s="10" t="s">
         <v>387</v>
       </c>
-      <c r="J68" s="15" t="s">
+      <c r="J68" s="10" t="s">
         <v>388</v>
       </c>
-      <c r="K68" s="15" t="s">
+      <c r="K68" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="L68" s="18" t="s">
+      <c r="L68" s="13" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="51" x14ac:dyDescent="0.25">
-      <c r="A69" s="12" t="s">
+      <c r="A69" s="7" t="s">
         <v>390</v>
       </c>
-      <c r="B69" s="9">
+      <c r="B69" s="7">
         <v>3</v>
       </c>
-      <c r="C69" s="12" t="s">
+      <c r="C69" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="D69" s="12" t="s">
+      <c r="D69" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="E69" s="12" t="s">
+      <c r="E69" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="F69" s="12"/>
-      <c r="G69" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H69" s="15" t="s">
+      <c r="F69" s="7"/>
+      <c r="G69" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="I69" s="15" t="s">
+      <c r="I69" s="10" t="s">
         <v>392</v>
       </c>
-      <c r="J69" s="15" t="s">
+      <c r="J69" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="K69" s="15" t="s">
+      <c r="K69" s="10" t="s">
         <v>394</v>
       </c>
-      <c r="L69" s="18" t="s">
+      <c r="L69" s="13" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="70" spans="1:12" ht="229.5" x14ac:dyDescent="0.25">
-      <c r="A70" s="12" t="s">
+      <c r="A70" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="B70" s="9">
+      <c r="B70" s="7">
         <v>3</v>
       </c>
-      <c r="C70" s="12" t="s">
+      <c r="C70" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="D70" s="12" t="s">
+      <c r="D70" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="E70" s="12" t="s">
+      <c r="E70" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="F70" s="12"/>
-      <c r="G70" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H70" s="15" t="s">
+      <c r="F70" s="7"/>
+      <c r="G70" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H70" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="I70" s="15" t="s">
+      <c r="I70" s="10" t="s">
         <v>398</v>
       </c>
-      <c r="J70" s="15" t="s">
+      <c r="J70" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="K70" s="15"/>
-      <c r="L70" s="18" t="s">
+      <c r="K70" s="10"/>
+      <c r="L70" s="13" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
-      <c r="A71" s="12" t="s">
+      <c r="A71" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="B71" s="9">
+      <c r="B71" s="7">
         <v>3</v>
       </c>
-      <c r="C71" s="12" t="s">
+      <c r="C71" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="D71" s="12" t="s">
+      <c r="D71" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="E71" s="12" t="s">
+      <c r="E71" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="F71" s="12"/>
-      <c r="G71" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H71" s="15" t="s">
+      <c r="F71" s="7"/>
+      <c r="G71" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>402</v>
       </c>
-      <c r="I71" s="15" t="s">
+      <c r="I71" s="10" t="s">
         <v>403</v>
       </c>
-      <c r="J71" s="15" t="s">
+      <c r="J71" s="10" t="s">
         <v>404</v>
       </c>
-      <c r="K71" s="15" t="s">
+      <c r="K71" s="10" t="s">
         <v>405</v>
       </c>
-      <c r="L71" s="18" t="s">
+      <c r="L71" s="13" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="140.25" x14ac:dyDescent="0.25">
-      <c r="A72" s="12" t="s">
+      <c r="A72" s="7" t="s">
         <v>407</v>
       </c>
-      <c r="B72" s="9">
+      <c r="B72" s="7">
         <v>3</v>
       </c>
-      <c r="C72" s="12" t="s">
+      <c r="C72" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="D72" s="12" t="s">
+      <c r="D72" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="E72" s="12" t="s">
+      <c r="E72" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="F72" s="12"/>
-      <c r="G72" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H72" s="15" t="s">
+      <c r="F72" s="7"/>
+      <c r="G72" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H72" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="I72" s="15" t="s">
+      <c r="I72" s="10" t="s">
         <v>409</v>
       </c>
-      <c r="J72" s="15" t="s">
+      <c r="J72" s="10" t="s">
         <v>410</v>
       </c>
-      <c r="K72" s="15"/>
-      <c r="L72" s="18" t="s">
+      <c r="K72" s="10"/>
+      <c r="L72" s="13" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="73" spans="1:12" ht="127.5" x14ac:dyDescent="0.25">
-      <c r="A73" s="12" t="s">
+      <c r="A73" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="B73" s="9">
+      <c r="B73" s="7">
         <v>3</v>
       </c>
-      <c r="C73" s="12" t="s">
+      <c r="C73" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="D73" s="12" t="s">
+      <c r="D73" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="E73" s="12" t="s">
+      <c r="E73" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="F73" s="12"/>
-      <c r="G73" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="H73" s="15" t="s">
+      <c r="F73" s="7"/>
+      <c r="G73" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>413</v>
       </c>
-      <c r="I73" s="15" t="s">
+      <c r="I73" s="10" t="s">
         <v>414</v>
       </c>
-      <c r="J73" s="15" t="s">
+      <c r="J73" s="10" t="s">
         <v>415</v>
       </c>
-      <c r="K73" s="15"/>
-      <c r="L73" s="18" t="s">
+      <c r="K73" s="10"/>
+      <c r="L73" s="13" t="s">
         <v>416</v>
       </c>
     </row>

--- a/NL2SPARQL_Evaluation_Dataset.xlsx
+++ b/NL2SPARQL_Evaluation_Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fersi\Desktop\NL2SPARQL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D9FE86-09D9-49A9-9DB8-090BB26A652D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46C3DAFD-788B-4BAE-B99C-509638B830AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="26640" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1277,9 +1277,6 @@
     <t>NEEDS LIVE VERIFICATION — not derivable from the 15-row KG sample; run the corresponding SPARQL against Fuseki and fill in. Same ambiguity as property_ambiguity_003, tested with Arabic-first phrasing (columns intentionally reordered to vary which language anchors the ambiguous phrase).</t>
   </si>
   <si>
-    <t>AUA</t>
-  </si>
-  <si>
     <t>ASP</t>
   </si>
   <si>
@@ -1329,6 +1326,9 @@
   </si>
   <si>
     <t>Chania International Airport, Kos International Airport "Ippokratis" (complete — Greece only has 2)</t>
+  </si>
+  <si>
+    <t>Mali Air</t>
   </si>
 </sst>
 </file>
@@ -2232,7 +2232,7 @@
         <v>79</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>417</v>
+        <v>434</v>
       </c>
       <c r="L7" s="13" t="s">
         <v>80</v>
@@ -2556,7 +2556,7 @@
         <v>130</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="L16" s="13" t="s">
         <v>131</v>
@@ -2700,7 +2700,7 @@
         <v>153</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="L20" s="12" t="s">
         <v>154</v>
@@ -3238,7 +3238,7 @@
         <v>227</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L35" s="13" t="s">
         <v>228</v>
@@ -3458,7 +3458,7 @@
         <v>257</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L41" s="13" t="s">
         <v>258</v>
@@ -3496,7 +3496,7 @@
         <v>262</v>
       </c>
       <c r="K42" s="10" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L42" s="13" t="s">
         <v>258</v>
@@ -3534,7 +3534,7 @@
         <v>266</v>
       </c>
       <c r="K43" s="10" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L43" s="13" t="s">
         <v>258</v>
@@ -3572,7 +3572,7 @@
         <v>271</v>
       </c>
       <c r="K44" s="10" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L44" s="13" t="s">
         <v>272</v>
@@ -3610,7 +3610,7 @@
         <v>276</v>
       </c>
       <c r="K45" s="10" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L45" s="13" t="s">
         <v>272</v>
@@ -3648,7 +3648,7 @@
         <v>280</v>
       </c>
       <c r="K46" s="10" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="L46" s="13" t="s">
         <v>272</v>
@@ -3686,7 +3686,7 @@
         <v>285</v>
       </c>
       <c r="K47" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="L47" s="13" t="s">
         <v>286</v>
@@ -3760,7 +3760,7 @@
         <v>294</v>
       </c>
       <c r="K49" s="10" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L49" s="13" t="s">
         <v>286</v>
@@ -3798,7 +3798,7 @@
         <v>299</v>
       </c>
       <c r="K50" s="10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L50" s="13" t="s">
         <v>300</v>
@@ -3836,7 +3836,7 @@
         <v>304</v>
       </c>
       <c r="K51" s="10" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L51" s="13" t="s">
         <v>300</v>
@@ -3874,7 +3874,7 @@
         <v>308</v>
       </c>
       <c r="K52" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L52" s="13" t="s">
         <v>300</v>
@@ -3912,7 +3912,7 @@
         <v>313</v>
       </c>
       <c r="K53" s="10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="L53" s="13" t="s">
         <v>314</v>
@@ -3950,7 +3950,7 @@
         <v>318</v>
       </c>
       <c r="K54" s="10" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L54" s="13" t="s">
         <v>314</v>
@@ -3988,7 +3988,7 @@
         <v>322</v>
       </c>
       <c r="K55" s="10" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L55" s="13" t="s">
         <v>314</v>

--- a/NL2SPARQL_Evaluation_Dataset.xlsx
+++ b/NL2SPARQL_Evaluation_Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fersi\Desktop\NL2SPARQL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46C3DAFD-788B-4BAE-B99C-509638B830AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732D3C96-5D2D-439D-B6FF-429162821199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="26640" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1981,7 +1981,7 @@
     <col min="7" max="7" width="12" style="8" customWidth="1"/>
     <col min="8" max="10" width="46" style="8" customWidth="1"/>
     <col min="11" max="11" width="46.42578125" style="8" customWidth="1"/>
-    <col min="12" max="12" width="30" style="5" customWidth="1"/>
+    <col min="12" max="12" width="56.140625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">

--- a/NL2SPARQL_Evaluation_Dataset.xlsx
+++ b/NL2SPARQL_Evaluation_Dataset.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fersi\Desktop\NL2SPARQL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732D3C96-5D2D-439D-B6FF-429162821199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA55B1C-FDEE-4572-B6B3-1C3EA4A7BB64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="26640" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="437">
   <si>
     <t>NL2SPARQL Evaluation Dataset — Legend</t>
   </si>
@@ -1329,13 +1329,19 @@
   </si>
   <si>
     <t>Mali Air</t>
+  </si>
+  <si>
+    <t>www.Department0.University0.edu</t>
+  </si>
+  <si>
+    <t>www.University0.edu</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1362,6 +1368,14 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1416,10 +1430,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1458,8 +1473,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2022,7 +2041,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>44</v>
       </c>
@@ -2130,7 +2149,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>64</v>
       </c>
@@ -2166,7 +2185,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>70</v>
       </c>
@@ -2202,7 +2221,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>76</v>
       </c>
@@ -2238,7 +2257,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>81</v>
       </c>
@@ -2274,7 +2293,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>86</v>
       </c>
@@ -2346,7 +2365,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>95</v>
       </c>
@@ -2382,7 +2401,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>103</v>
       </c>
@@ -2490,7 +2509,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>121</v>
       </c>
@@ -2526,7 +2545,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>127</v>
       </c>
@@ -2634,7 +2653,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>141</v>
       </c>
@@ -2670,7 +2689,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>147</v>
       </c>
@@ -2706,7 +2725,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>155</v>
       </c>
@@ -2742,7 +2761,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>161</v>
       </c>
@@ -2778,7 +2797,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>166</v>
       </c>
@@ -2814,7 +2833,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>170</v>
       </c>
@@ -2850,7 +2869,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>174</v>
       </c>
@@ -2886,7 +2905,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>180</v>
       </c>
@@ -2922,7 +2941,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>185</v>
       </c>
@@ -2958,7 +2977,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>189</v>
       </c>
@@ -2994,7 +3013,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>194</v>
       </c>
@@ -3030,7 +3049,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>199</v>
       </c>
@@ -3066,7 +3085,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>204</v>
       </c>
@@ -3102,7 +3121,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>208</v>
       </c>
@@ -3136,7 +3155,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>214</v>
       </c>
@@ -3172,7 +3191,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>219</v>
       </c>
@@ -3208,7 +3227,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>224</v>
       </c>
@@ -3244,7 +3263,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
         <v>229</v>
       </c>
@@ -3278,7 +3297,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
         <v>234</v>
       </c>
@@ -3312,7 +3331,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
         <v>238</v>
       </c>
@@ -3350,7 +3369,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>245</v>
       </c>
@@ -3388,7 +3407,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>249</v>
       </c>
@@ -3426,7 +3445,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>253</v>
       </c>
@@ -3464,7 +3483,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>259</v>
       </c>
@@ -3502,7 +3521,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
         <v>263</v>
       </c>
@@ -3540,7 +3559,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
         <v>267</v>
       </c>
@@ -3578,7 +3597,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>273</v>
       </c>
@@ -3616,7 +3635,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>277</v>
       </c>
@@ -3692,7 +3711,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
         <v>287</v>
       </c>
@@ -3728,7 +3747,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
         <v>291</v>
       </c>
@@ -3766,7 +3785,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>295</v>
       </c>
@@ -3804,7 +3823,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
         <v>301</v>
       </c>
@@ -3842,7 +3861,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
         <v>305</v>
       </c>
@@ -3880,7 +3899,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
         <v>309</v>
       </c>
@@ -3918,7 +3937,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
         <v>315</v>
       </c>
@@ -3956,7 +3975,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
         <v>319</v>
       </c>
@@ -3994,7 +4013,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
         <v>323</v>
       </c>
@@ -4028,7 +4047,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
         <v>330</v>
       </c>
@@ -4062,7 +4081,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
         <v>334</v>
       </c>
@@ -4096,7 +4115,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
         <v>338</v>
       </c>
@@ -4132,7 +4151,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
         <v>346</v>
       </c>
@@ -4168,7 +4187,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
         <v>351</v>
       </c>
@@ -4204,7 +4223,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
         <v>357</v>
       </c>
@@ -4240,7 +4259,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
         <v>362</v>
       </c>
@@ -4276,7 +4295,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
         <v>370</v>
       </c>
@@ -4312,7 +4331,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
         <v>374</v>
       </c>
@@ -4348,7 +4367,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
         <v>377</v>
       </c>
@@ -4384,7 +4403,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
         <v>381</v>
       </c>
@@ -4420,7 +4439,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
         <v>385</v>
       </c>
@@ -4456,7 +4475,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
         <v>390</v>
       </c>
@@ -4492,7 +4511,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="229.5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
         <v>395</v>
       </c>
@@ -4521,12 +4540,14 @@
       <c r="J70" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="K70" s="10"/>
+      <c r="K70" s="16" t="s">
+        <v>435</v>
+      </c>
       <c r="L70" s="13" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
         <v>401</v>
       </c>
@@ -4562,7 +4583,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="140.25" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
         <v>407</v>
       </c>
@@ -4591,12 +4612,14 @@
       <c r="J72" s="10" t="s">
         <v>410</v>
       </c>
-      <c r="K72" s="10"/>
+      <c r="K72" s="16" t="s">
+        <v>436</v>
+      </c>
       <c r="L72" s="13" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="127.5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
         <v>412</v>
       </c>
@@ -4625,7 +4648,9 @@
       <c r="J73" s="10" t="s">
         <v>415</v>
       </c>
-      <c r="K73" s="10"/>
+      <c r="K73" s="16" t="s">
+        <v>436</v>
+      </c>
       <c r="L73" s="13" t="s">
         <v>416</v>
       </c>
@@ -4637,6 +4662,11 @@
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="K70" r:id="rId1" xr:uid="{6CB27492-1D92-4B99-A7F3-01287A15D6DE}"/>
+    <hyperlink ref="K72" r:id="rId2" xr:uid="{9F4442FC-B522-4DDC-870A-D72EE6646221}"/>
+    <hyperlink ref="K73" r:id="rId3" xr:uid="{449ABBF1-A75A-427C-A17A-36A01AB0C463}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/NL2SPARQL_Evaluation_Dataset.xlsx
+++ b/NL2SPARQL_Evaluation_Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fersi\Desktop\NL2SPARQL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA55B1C-FDEE-4572-B6B3-1C3EA4A7BB64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D30F87-DD4C-4462-9B8B-557A291D89A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="26640" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="436">
   <si>
     <t>NL2SPARQL Evaluation Dataset — Legend</t>
   </si>
@@ -1331,10 +1331,7 @@
     <t>Mali Air</t>
   </si>
   <si>
-    <t>www.Department0.University0.edu</t>
-  </si>
-  <si>
-    <t>www.University0.edu</t>
+    <t>Department0</t>
   </si>
 </sst>
 </file>
@@ -1471,11 +1468,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -1787,12 +1784,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -4540,7 +4537,7 @@
       <c r="J70" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="K70" s="16" t="s">
+      <c r="K70" s="14" t="s">
         <v>435</v>
       </c>
       <c r="L70" s="13" t="s">
@@ -4612,8 +4609,8 @@
       <c r="J72" s="10" t="s">
         <v>410</v>
       </c>
-      <c r="K72" s="16" t="s">
-        <v>436</v>
+      <c r="K72" s="14" t="s">
+        <v>405</v>
       </c>
       <c r="L72" s="13" t="s">
         <v>411</v>
@@ -4648,8 +4645,8 @@
       <c r="J73" s="10" t="s">
         <v>415</v>
       </c>
-      <c r="K73" s="16" t="s">
-        <v>436</v>
+      <c r="K73" s="14" t="s">
+        <v>405</v>
       </c>
       <c r="L73" s="13" t="s">
         <v>416</v>
@@ -4663,9 +4660,9 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="K70" r:id="rId1" xr:uid="{6CB27492-1D92-4B99-A7F3-01287A15D6DE}"/>
-    <hyperlink ref="K72" r:id="rId2" xr:uid="{9F4442FC-B522-4DDC-870A-D72EE6646221}"/>
-    <hyperlink ref="K73" r:id="rId3" xr:uid="{449ABBF1-A75A-427C-A17A-36A01AB0C463}"/>
+    <hyperlink ref="K70" r:id="rId1" display="www.Department0.University0.edu" xr:uid="{6CB27492-1D92-4B99-A7F3-01287A15D6DE}"/>
+    <hyperlink ref="K72" r:id="rId2" display="www.University0.edu" xr:uid="{9F4442FC-B522-4DDC-870A-D72EE6646221}"/>
+    <hyperlink ref="K73" r:id="rId3" display="www.University0.edu" xr:uid="{449ABBF1-A75A-427C-A17A-36A01AB0C463}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/NL2SPARQL_Evaluation_Dataset.xlsx
+++ b/NL2SPARQL_Evaluation_Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fersi\Desktop\NL2SPARQL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D30F87-DD4C-4462-9B8B-557A291D89A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB16A24B-3DF6-46A3-B698-DCFDF732B1BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="26640" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1316,9 +1316,6 @@
     <t>ESB, SOF, SBZ, MUC, ZRH, EBL, ACH, STR, LUX, GRZ</t>
   </si>
   <si>
-    <t>EBL, JFK, CDG, CDG, IST, IST, BER, FRA, FRA, FRA</t>
-  </si>
-  <si>
     <t>PFO, CTA, BOM, RIX, PMI, CPH, FCO, JFK, BCN, GYD</t>
   </si>
   <si>
@@ -1332,6 +1329,9 @@
   </si>
   <si>
     <t>Department0</t>
+  </si>
+  <si>
+    <t>EBL, JFK, CDG, IST, BER, BKK, FRA, GYD, LUX, MUC, NRT, FCO, LHR, CGN, HAJ, ESB, ZRH, WAW, HAM, ORY, BRU, BCN, CPH, LEJ, SOF, VIE, SAW, BOM, OTP, BEG, MRS, HEL, RMF, AYT, MLA, CHQ, STR, PMO, LGW, ARN, VCE, PMI, ZAG, RIX</t>
   </si>
 </sst>
 </file>
@@ -2248,7 +2248,7 @@
         <v>79</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L7" s="13" t="s">
         <v>80</v>
@@ -3594,7 +3594,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>273</v>
       </c>
@@ -3626,7 +3626,7 @@
         <v>276</v>
       </c>
       <c r="K45" s="10" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="L45" s="13" t="s">
         <v>272</v>
@@ -3664,7 +3664,7 @@
         <v>280</v>
       </c>
       <c r="K46" s="10" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L46" s="13" t="s">
         <v>272</v>
@@ -3702,7 +3702,7 @@
         <v>285</v>
       </c>
       <c r="K47" s="10" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="L47" s="13" t="s">
         <v>286</v>
@@ -3776,7 +3776,7 @@
         <v>294</v>
       </c>
       <c r="K49" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="L49" s="13" t="s">
         <v>286</v>
@@ -4538,7 +4538,7 @@
         <v>399</v>
       </c>
       <c r="K70" s="14" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="L70" s="13" t="s">
         <v>400</v>

--- a/NL2SPARQL_Evaluation_Dataset.xlsx
+++ b/NL2SPARQL_Evaluation_Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fersi\Desktop\NL2SPARQL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB16A24B-3DF6-46A3-B698-DCFDF732B1BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60CC941B-84D0-4FEE-9563-7B92CFEAB92D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="26640" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="440">
   <si>
     <t>NL2SPARQL Evaluation Dataset — Legend</t>
   </si>
@@ -1304,9 +1304,6 @@
     <t>SOF is higher (CHQ: 490, SOF: 1742)</t>
   </si>
   <si>
-    <t>AI180, PC904, OS631, BR62, OS830, OS315, OS631, 7L280, OS87, OS52 (top 10 by gspeed, highest first)</t>
-  </si>
-  <si>
     <t>LO225, TO4388, EW9754, FR6889, OU442, FR1589, OS462, AY1475, PE106, FR947</t>
   </si>
   <si>
@@ -1332,6 +1329,21 @@
   </si>
   <si>
     <t>EBL, JFK, CDG, IST, BER, BKK, FRA, GYD, LUX, MUC, NRT, FCO, LHR, CGN, HAJ, ESB, ZRH, WAW, HAM, ORY, BRU, BCN, CPH, LEJ, SOF, VIE, SAW, BOM, OTP, BEG, MRS, HEL, RMF, AYT, MLA, CHQ, STR, PMO, LGW, ARN, VCE, PMI, ZAG, RIX</t>
+  </si>
+  <si>
+    <t>SP-RSD</t>
+  </si>
+  <si>
+    <t>TC-LSS, TC-JOG, TC-LSP, TC-LUP, TC-JOB</t>
+  </si>
+  <si>
+    <t>ACH, ARN, AYT, BCN, BEG, BER, BKK, BLQ, BOM, BRI, BRU, CDG, CGN, CHQ, CPH, CTA, EBL, ESB, FCO, FRA, GRZ, GYD, HAJ, HAM, HEL, IST, JFK, KGS, LCA, LGW, LHR, LUX, MLA, MRS, NAP, NRT, ORY, OTP, PFO, PMI, PMO, RIX, RMF, SOF, STR, TIA, VCE, VIE, WAW, ZAG</t>
+  </si>
+  <si>
+    <t>AI180, PC904, OS631, BR62, OS315, OS830, 7L280, OS52, OS87, DE1866, OS235, OS305, TK1887, FR1565, OS214, FR9889, FR1588, TO4388, SM2993, PE106, KE537, FR4433, LO225, OS487, OS549, FR6890, DE1170, BT273, OS529, OS786, FR9005, OS543</t>
+  </si>
+  <si>
+    <t>ARN, AYT, BCN, BEG, BER, BKK, BLQ, BOM, BRI, BRU, CDG, CGN, CHQ, CPH, CTA, DUS, EBL, ESB, FCO, FRA, GRZ, GYD, HAJ, HAM, HEL, IST, JFK, KGS, KRK, LCA, LEJ, LGW, LHR, LUX, MLA, MRS, MUC, NAP, NRT, ORY, OTP, PFO, PMI, PMO, RIX, RMF, SAW, SBZ, SOF, STR, TIA, VCE, VIE, WAW, ZAG, ZRH</t>
   </si>
 </sst>
 </file>
@@ -2248,7 +2260,7 @@
         <v>79</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="L7" s="13" t="s">
         <v>80</v>
@@ -3147,7 +3159,9 @@
       <c r="J32" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="K32" s="10"/>
+      <c r="K32" s="10" t="s">
+        <v>435</v>
+      </c>
       <c r="L32" s="13" t="s">
         <v>213</v>
       </c>
@@ -3260,7 +3274,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
         <v>229</v>
       </c>
@@ -3289,7 +3303,9 @@
       <c r="J36" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="K36" s="10"/>
+      <c r="K36" s="10" t="s">
+        <v>437</v>
+      </c>
       <c r="L36" s="13" t="s">
         <v>233</v>
       </c>
@@ -3323,7 +3339,9 @@
       <c r="J37" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="K37" s="10"/>
+      <c r="K37" s="10" t="s">
+        <v>436</v>
+      </c>
       <c r="L37" s="13" t="s">
         <v>213</v>
       </c>
@@ -3442,7 +3460,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>253</v>
       </c>
@@ -3474,7 +3492,7 @@
         <v>257</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="L41" s="13" t="s">
         <v>258</v>
@@ -3512,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="K42" s="10" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L42" s="13" t="s">
         <v>258</v>
@@ -3550,7 +3568,7 @@
         <v>266</v>
       </c>
       <c r="K43" s="10" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L43" s="13" t="s">
         <v>258</v>
@@ -3588,7 +3606,7 @@
         <v>271</v>
       </c>
       <c r="K44" s="10" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L44" s="13" t="s">
         <v>272</v>
@@ -3626,7 +3644,7 @@
         <v>276</v>
       </c>
       <c r="K45" s="10" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="L45" s="13" t="s">
         <v>272</v>
@@ -3664,7 +3682,7 @@
         <v>280</v>
       </c>
       <c r="K46" s="10" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L46" s="13" t="s">
         <v>272</v>
@@ -3702,13 +3720,13 @@
         <v>285</v>
       </c>
       <c r="K47" s="10" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L47" s="13" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
         <v>287</v>
       </c>
@@ -3739,7 +3757,9 @@
       <c r="J48" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="K48" s="10"/>
+      <c r="K48" s="10" t="s">
+        <v>439</v>
+      </c>
       <c r="L48" s="13" t="s">
         <v>286</v>
       </c>
@@ -3776,7 +3796,7 @@
         <v>294</v>
       </c>
       <c r="K49" s="10" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="L49" s="13" t="s">
         <v>286</v>
@@ -4538,7 +4558,7 @@
         <v>399</v>
       </c>
       <c r="K70" s="14" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L70" s="13" t="s">
         <v>400</v>
